--- a/database/event/8046/event_8046_evp_summary.xlsx
+++ b/database/event/8046/event_8046_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.3267</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.3403</v>
       </c>
       <c r="D2" t="n">
         <v>4.1544</v>
@@ -545,7 +545,7 @@
         <v>10.5033</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.1702</v>
       </c>
       <c r="D3" t="n">
         <v>3.8217</v>
@@ -591,7 +591,7 @@
         <v>7.8819</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.6286</v>
       </c>
       <c r="D4" t="n">
         <v>2.7628</v>
@@ -637,7 +637,7 @@
         <v>6.934</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.4327</v>
       </c>
       <c r="D5" t="n">
         <v>2.3798</v>
@@ -683,7 +683,7 @@
         <v>5.7613</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.1904</v>
       </c>
       <c r="D6" t="n">
         <v>1.9061</v>
@@ -729,7 +729,7 @@
         <v>5.415</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.1188</v>
       </c>
       <c r="D7" t="n">
         <v>1.7662</v>
@@ -775,7 +775,7 @@
         <v>5.4067</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.1171</v>
       </c>
       <c r="D8" t="n">
         <v>1.7628</v>
@@ -821,7 +821,7 @@
         <v>5.2979</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.0947</v>
       </c>
       <c r="D9" t="n">
         <v>1.7189</v>
@@ -867,7 +867,7 @@
         <v>5.042</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.0418</v>
       </c>
       <c r="D10" t="n">
         <v>1.6155</v>
@@ -913,7 +913,7 @@
         <v>4.8526</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.0026</v>
       </c>
       <c r="D11" t="n">
         <v>1.539</v>
@@ -959,7 +959,7 @@
         <v>4.584</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>1.4305</v>
@@ -1005,7 +1005,7 @@
         <v>4.3429</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.8973</v>
       </c>
       <c r="D13" t="n">
         <v>1.3331</v>
@@ -1051,7 +1051,7 @@
         <v>4.3084</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8902</v>
       </c>
       <c r="D14" t="n">
         <v>1.3191</v>
@@ -1097,7 +1097,7 @@
         <v>4.2182</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.8716</v>
       </c>
       <c r="D15" t="n">
         <v>1.2827</v>
@@ -1143,7 +1143,7 @@
         <v>3.7888</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>1.1092</v>
@@ -1189,7 +1189,7 @@
         <v>3.7634</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.7776</v>
       </c>
       <c r="D17" t="n">
         <v>1.099</v>
@@ -1235,7 +1235,7 @@
         <v>3.747</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.7742</v>
       </c>
       <c r="D18" t="n">
         <v>1.0923</v>
@@ -1281,7 +1281,7 @@
         <v>3.4567</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>0.9751</v>
@@ -1327,7 +1327,7 @@
         <v>3.4362</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="D20" t="n">
         <v>0.9668</v>
@@ -1373,7 +1373,7 @@
         <v>3.4125</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="D21" t="n">
         <v>0.9572000000000001</v>
@@ -1419,7 +1419,7 @@
         <v>3.3213</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.6862</v>
       </c>
       <c r="D22" t="n">
         <v>0.9204</v>
@@ -1465,7 +1465,7 @@
         <v>3.3001</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.6819</v>
       </c>
       <c r="D23" t="n">
         <v>0.9118000000000001</v>
@@ -1511,7 +1511,7 @@
         <v>3.2257</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.6665</v>
       </c>
       <c r="D24" t="n">
         <v>0.8817</v>
@@ -1557,7 +1557,7 @@
         <v>3.0542</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.6311</v>
       </c>
       <c r="D25" t="n">
         <v>0.8125</v>
@@ -1603,7 +1603,7 @@
         <v>2.8072</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="D26" t="n">
         <v>0.7127</v>
@@ -1649,7 +1649,7 @@
         <v>2.696</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="D27" t="n">
         <v>0.6677999999999999</v>
@@ -1695,7 +1695,7 @@
         <v>2.6593</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5495</v>
       </c>
       <c r="D28" t="n">
         <v>0.6529</v>
@@ -1741,7 +1741,7 @@
         <v>2.6058</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.5384</v>
       </c>
       <c r="D29" t="n">
         <v>0.6313</v>
@@ -1787,7 +1787,7 @@
         <v>2.3457</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.4847</v>
       </c>
       <c r="D30" t="n">
         <v>0.5262</v>
@@ -1833,7 +1833,7 @@
         <v>2.0955</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="D31" t="n">
         <v>0.4252</v>
@@ -1879,7 +1879,7 @@
         <v>2.065</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.4267</v>
       </c>
       <c r="D32" t="n">
         <v>0.4129</v>
@@ -1925,7 +1925,7 @@
         <v>2.0077</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.4148</v>
       </c>
       <c r="D33" t="n">
         <v>0.3897</v>
@@ -1971,7 +1971,7 @@
         <v>1.9111</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.3949</v>
       </c>
       <c r="D34" t="n">
         <v>0.3507</v>
@@ -2017,7 +2017,7 @@
         <v>1.8843</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.3893</v>
       </c>
       <c r="D35" t="n">
         <v>0.3399</v>
@@ -2063,7 +2063,7 @@
         <v>1.836</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.3794</v>
       </c>
       <c r="D36" t="n">
         <v>0.3203</v>
@@ -2109,7 +2109,7 @@
         <v>1.8005</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="D37" t="n">
         <v>0.306</v>
@@ -2155,7 +2155,7 @@
         <v>1.7767</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3671</v>
       </c>
       <c r="D38" t="n">
         <v>0.2964</v>
@@ -2201,7 +2201,7 @@
         <v>1.7373</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.359</v>
       </c>
       <c r="D39" t="n">
         <v>0.2805</v>
@@ -2247,7 +2247,7 @@
         <v>1.5093</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3119</v>
       </c>
       <c r="D40" t="n">
         <v>0.1884</v>
@@ -2293,7 +2293,7 @@
         <v>1.5074</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="D41" t="n">
         <v>0.1876</v>
@@ -2339,7 +2339,7 @@
         <v>1.4546</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3005</v>
       </c>
       <c r="D42" t="n">
         <v>0.1663</v>
@@ -2385,7 +2385,7 @@
         <v>1.4187</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2931</v>
       </c>
       <c r="D43" t="n">
         <v>0.1518</v>
@@ -2431,7 +2431,7 @@
         <v>1.4176</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2929</v>
       </c>
       <c r="D44" t="n">
         <v>0.1513</v>
@@ -2477,7 +2477,7 @@
         <v>1.3642</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2819</v>
       </c>
       <c r="D45" t="n">
         <v>0.1297</v>
@@ -2523,7 +2523,7 @@
         <v>1.2744</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2633</v>
       </c>
       <c r="D46" t="n">
         <v>0.0935</v>
@@ -2569,7 +2569,7 @@
         <v>1.0739</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2219</v>
       </c>
       <c r="D47" t="n">
         <v>0.0125</v>
@@ -2615,7 +2615,7 @@
         <v>1.073</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2217</v>
       </c>
       <c r="D48" t="n">
         <v>0.0121</v>
@@ -2661,7 +2661,7 @@
         <v>0.9744</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2013</v>
       </c>
       <c r="D49" t="n">
         <v>-0.0277</v>
@@ -2707,7 +2707,7 @@
         <v>0.8218</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1698</v>
       </c>
       <c r="D50" t="n">
         <v>-0.08939999999999999</v>
@@ -2753,7 +2753,7 @@
         <v>0.6148</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="D51" t="n">
         <v>-0.173</v>
@@ -2799,7 +2799,7 @@
         <v>0.5264</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
       <c r="D52" t="n">
         <v>-0.2087</v>
@@ -2845,7 +2845,7 @@
         <v>0.1398</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3649</v>
@@ -2891,7 +2891,7 @@
         <v>0.125</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0258</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3709</v>
@@ -2937,7 +2937,7 @@
         <v>0.1191</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0246</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3732</v>
@@ -2983,7 +2983,7 @@
         <v>-0.0051</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0011</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4234</v>
@@ -3029,7 +3029,7 @@
         <v>-0.1079</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.0223</v>
       </c>
       <c r="D57" t="n">
         <v>-0.465</v>
@@ -3075,7 +3075,7 @@
         <v>-0.137</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.0283</v>
       </c>
       <c r="D58" t="n">
         <v>-0.4767</v>
@@ -3121,7 +3121,7 @@
         <v>-0.2646</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.0547</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5283</v>
@@ -3167,7 +3167,7 @@
         <v>-0.277</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.0572</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5333</v>
@@ -3213,7 +3213,7 @@
         <v>-0.3429</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.0709</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5599</v>
@@ -3259,7 +3259,7 @@
         <v>-0.4307</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.089</v>
       </c>
       <c r="D62" t="n">
         <v>-0.5954</v>
@@ -3305,7 +3305,7 @@
         <v>-0.4838</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6168</v>
@@ -3351,7 +3351,7 @@
         <v>-0.5151</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.1064</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6294999999999999</v>
@@ -3397,7 +3397,7 @@
         <v>-0.5236</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.1082</v>
       </c>
       <c r="D65" t="n">
         <v>-0.6329</v>
@@ -3443,7 +3443,7 @@
         <v>-0.6292</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="D66" t="n">
         <v>-0.6755</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8489</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.1754</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7643</v>
@@ -3535,7 +3535,7 @@
         <v>-0.886</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.1831</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7793</v>
@@ -3581,7 +3581,7 @@
         <v>-1</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.2066</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8253</v>
@@ -3627,7 +3627,7 @@
         <v>-1.3278</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.2744</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9578</v>
@@ -3673,7 +3673,7 @@
         <v>-1.5858</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.3277</v>
       </c>
       <c r="D71" t="n">
         <v>-1.062</v>
@@ -3719,7 +3719,7 @@
         <v>-1.7216</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.3557</v>
       </c>
       <c r="D72" t="n">
         <v>-1.1169</v>
@@ -3765,7 +3765,7 @@
         <v>-1.7544</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.3625</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1301</v>
@@ -3811,7 +3811,7 @@
         <v>-1.921</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.3969</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1974</v>
@@ -3857,7 +3857,7 @@
         <v>-1.9306</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.3989</v>
       </c>
       <c r="D75" t="n">
         <v>-1.2013</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9748</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.408</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2191</v>
@@ -3949,7 +3949,7 @@
         <v>-2.0829</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.4304</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2628</v>
@@ -3995,7 +3995,7 @@
         <v>-2.5401</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.5248</v>
       </c>
       <c r="D78" t="n">
         <v>-1.4475</v>
@@ -4041,7 +4041,7 @@
         <v>-2.6136</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.54</v>
       </c>
       <c r="D79" t="n">
         <v>-1.4772</v>
@@ -4087,7 +4087,7 @@
         <v>-2.6803</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-0.5538</v>
       </c>
       <c r="D80" t="n">
         <v>-1.5041</v>
@@ -4133,7 +4133,7 @@
         <v>-2.7916</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-0.5768</v>
       </c>
       <c r="D81" t="n">
         <v>-1.5491</v>
@@ -4179,7 +4179,7 @@
         <v>-5.1492</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-1.0639</v>
       </c>
       <c r="D82" t="n">
         <v>-2.5015</v>

--- a/database/event/8046/event_8046_evp_summary.xlsx
+++ b/database/event/8046/event_8046_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.3267</v>
+        <v>11.3152</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3403</v>
+        <v>2.3379</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1544</v>
+        <v>4.0641</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3267</v>
+        <v>11.3152</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5332</v>
+        <v>4.5218</v>
       </c>
       <c r="G2" t="n">
         <v>6.7935</v>
       </c>
       <c r="H2" t="n">
-        <v>4.805</v>
+        <v>4.7871</v>
       </c>
       <c r="I2" t="n">
         <v>4.8274</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.5033</v>
+        <v>10.4914</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1702</v>
+        <v>2.1677</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8217</v>
+        <v>3.7359</v>
       </c>
       <c r="E3" t="n">
-        <v>10.5033</v>
+        <v>10.4914</v>
       </c>
       <c r="F3" t="n">
-        <v>4.653</v>
+        <v>4.6411</v>
       </c>
       <c r="G3" t="n">
         <v>5.8503</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9928</v>
+        <v>4.9742</v>
       </c>
       <c r="I3" t="n">
         <v>5.016</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.8819</v>
+        <v>7.8538</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6286</v>
+        <v>1.6228</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7628</v>
+        <v>2.685</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8819</v>
+        <v>7.8538</v>
       </c>
       <c r="F4" t="n">
-        <v>5.2412</v>
+        <v>5.2131</v>
       </c>
       <c r="G4" t="n">
         <v>2.6406</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9152</v>
+        <v>5.8711</v>
       </c>
       <c r="I4" t="n">
         <v>5.9704</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.934</v>
+        <v>6.9076</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4327</v>
+        <v>1.4273</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3798</v>
+        <v>2.3081</v>
       </c>
       <c r="E5" t="n">
-        <v>6.934</v>
+        <v>6.9076</v>
       </c>
       <c r="F5" t="n">
-        <v>5.0175</v>
+        <v>4.9911</v>
       </c>
       <c r="G5" t="n">
         <v>1.9165</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5643</v>
+        <v>5.5229</v>
       </c>
       <c r="I5" t="n">
         <v>5.6163</v>
@@ -686,7 +686,7 @@
         <v>1.1904</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9061</v>
+        <v>1.8514</v>
       </c>
       <c r="E6" t="n">
         <v>5.7613</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.415</v>
+        <v>5.4065</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1188</v>
+        <v>1.1171</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7662</v>
+        <v>1.71</v>
       </c>
       <c r="E7" t="n">
-        <v>5.415</v>
+        <v>5.4065</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2563</v>
+        <v>2.2479</v>
       </c>
       <c r="G7" t="n">
         <v>3.1587</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2563</v>
+        <v>2.2479</v>
       </c>
       <c r="I7" t="n">
         <v>2.2668</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4067</v>
+        <v>5.3792</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1171</v>
+        <v>1.1115</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7628</v>
+        <v>1.6992</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4067</v>
+        <v>5.3792</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6988</v>
+        <v>3.6713</v>
       </c>
       <c r="G8" t="n">
         <v>1.7079</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6988</v>
+        <v>3.6713</v>
       </c>
       <c r="I8" t="n">
         <v>3.7334</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.2979</v>
+        <v>5.2764</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0947</v>
+        <v>1.0902</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7189</v>
+        <v>1.6582</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2979</v>
+        <v>5.2764</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8872</v>
+        <v>2.8657</v>
       </c>
       <c r="G9" t="n">
         <v>2.4107</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8872</v>
+        <v>2.8657</v>
       </c>
       <c r="I9" t="n">
         <v>2.9141</v>
@@ -870,7 +870,7 @@
         <v>1.0418</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6155</v>
+        <v>1.5648</v>
       </c>
       <c r="E10" t="n">
         <v>5.042</v>
@@ -916,7 +916,7 @@
         <v>1.0026</v>
       </c>
       <c r="D11" t="n">
-        <v>1.539</v>
+        <v>1.4894</v>
       </c>
       <c r="E11" t="n">
         <v>4.8526</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.584</v>
+        <v>4.5565</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9415</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4305</v>
+        <v>1.3714</v>
       </c>
       <c r="E12" t="n">
-        <v>4.584</v>
+        <v>4.5565</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1555</v>
+        <v>5.128</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5715</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7807</v>
+        <v>5.7377</v>
       </c>
       <c r="I12" t="n">
         <v>5.8346</v>
@@ -1008,7 +1008,7 @@
         <v>0.8973</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3331</v>
+        <v>1.2863</v>
       </c>
       <c r="E13" t="n">
         <v>4.3429</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.3084</v>
+        <v>4.306</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8902</v>
+        <v>0.8897</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3191</v>
+        <v>1.2716</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3084</v>
+        <v>4.306</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3155</v>
+        <v>0.3131</v>
       </c>
       <c r="G14" t="n">
         <v>3.9929</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3155</v>
+        <v>0.3131</v>
       </c>
       <c r="I14" t="n">
         <v>0.3184</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.2182</v>
+        <v>4.1957</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8716</v>
+        <v>0.8669</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2827</v>
+        <v>1.2277</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2182</v>
+        <v>4.1957</v>
       </c>
       <c r="F15" t="n">
-        <v>4.488</v>
+        <v>4.4655</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2698</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7341</v>
+        <v>4.6988</v>
       </c>
       <c r="I15" t="n">
         <v>4.7782</v>
@@ -1146,7 +1146,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1092</v>
+        <v>1.0655</v>
       </c>
       <c r="E16" t="n">
         <v>3.7888</v>
@@ -1192,7 +1192,7 @@
         <v>0.7776</v>
       </c>
       <c r="D17" t="n">
-        <v>1.099</v>
+        <v>1.0554</v>
       </c>
       <c r="E17" t="n">
         <v>3.7634</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.747</v>
+        <v>3.7356</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7742</v>
+        <v>0.7719</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0923</v>
+        <v>1.0444</v>
       </c>
       <c r="E18" t="n">
-        <v>3.747</v>
+        <v>3.7356</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0488</v>
+        <v>3.0374</v>
       </c>
       <c r="G18" t="n">
         <v>0.6982</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0488</v>
+        <v>3.0374</v>
       </c>
       <c r="I18" t="n">
         <v>3.0629</v>
@@ -1284,7 +1284,7 @@
         <v>0.7141999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9751</v>
+        <v>0.9332</v>
       </c>
       <c r="E19" t="n">
         <v>3.4567</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.4362</v>
+        <v>3.4252</v>
       </c>
       <c r="C20" t="n">
-        <v>0.71</v>
+        <v>0.7077</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9668</v>
+        <v>0.9207</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4362</v>
+        <v>3.4252</v>
       </c>
       <c r="F20" t="n">
-        <v>4.4362</v>
+        <v>4.4252</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.653</v>
+        <v>4.6356</v>
       </c>
       <c r="I20" t="n">
         <v>4.6746</v>
@@ -1376,7 +1376,7 @@
         <v>0.7050999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9156</v>
       </c>
       <c r="E21" t="n">
         <v>3.4125</v>
@@ -1422,7 +1422,7 @@
         <v>0.6862</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9204</v>
+        <v>0.8793</v>
       </c>
       <c r="E22" t="n">
         <v>3.3213</v>
@@ -1468,7 +1468,7 @@
         <v>0.6819</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8708</v>
       </c>
       <c r="E23" t="n">
         <v>3.3001</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2257</v>
+        <v>3.2131</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6665</v>
+        <v>0.6639</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8817</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2257</v>
+        <v>3.2131</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7001</v>
+        <v>1.6875</v>
       </c>
       <c r="G24" t="n">
         <v>1.5256</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7001</v>
+        <v>1.6875</v>
       </c>
       <c r="I24" t="n">
         <v>1.716</v>
@@ -1560,7 +1560,7 @@
         <v>0.6311</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8125</v>
+        <v>0.7729</v>
       </c>
       <c r="E25" t="n">
         <v>3.0542</v>
@@ -1606,7 +1606,7 @@
         <v>0.58</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7127</v>
+        <v>0.6745</v>
       </c>
       <c r="E26" t="n">
         <v>2.8072</v>
@@ -1652,7 +1652,7 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6302</v>
       </c>
       <c r="E27" t="n">
         <v>2.696</v>
@@ -1698,7 +1698,7 @@
         <v>0.5495</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6529</v>
+        <v>0.6156</v>
       </c>
       <c r="E28" t="n">
         <v>2.6593</v>
@@ -1744,7 +1744,7 @@
         <v>0.5384</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6313</v>
+        <v>0.5942</v>
       </c>
       <c r="E29" t="n">
         <v>2.6058</v>
@@ -1790,7 +1790,7 @@
         <v>0.4847</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5262</v>
+        <v>0.4906</v>
       </c>
       <c r="E30" t="n">
         <v>2.3457</v>
@@ -1836,7 +1836,7 @@
         <v>0.433</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4252</v>
+        <v>0.3909</v>
       </c>
       <c r="E31" t="n">
         <v>2.0955</v>
@@ -1882,7 +1882,7 @@
         <v>0.4267</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4129</v>
+        <v>0.3788</v>
       </c>
       <c r="E32" t="n">
         <v>2.065</v>
@@ -1928,7 +1928,7 @@
         <v>0.4148</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3897</v>
+        <v>0.356</v>
       </c>
       <c r="E33" t="n">
         <v>2.0077</v>
@@ -1974,7 +1974,7 @@
         <v>0.3949</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3507</v>
+        <v>0.3175</v>
       </c>
       <c r="E34" t="n">
         <v>1.9111</v>
@@ -2020,7 +2020,7 @@
         <v>0.3893</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3399</v>
+        <v>0.3068</v>
       </c>
       <c r="E35" t="n">
         <v>1.8843</v>
@@ -2066,7 +2066,7 @@
         <v>0.3794</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3203</v>
+        <v>0.2876</v>
       </c>
       <c r="E36" t="n">
         <v>1.836</v>
@@ -2112,7 +2112,7 @@
         <v>0.372</v>
       </c>
       <c r="D37" t="n">
-        <v>0.306</v>
+        <v>0.2734</v>
       </c>
       <c r="E37" t="n">
         <v>1.8005</v>
@@ -2158,7 +2158,7 @@
         <v>0.3671</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2964</v>
+        <v>0.2639</v>
       </c>
       <c r="E38" t="n">
         <v>1.7767</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.7373</v>
+        <v>1.733</v>
       </c>
       <c r="C39" t="n">
-        <v>0.359</v>
+        <v>0.3581</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2805</v>
+        <v>0.2465</v>
       </c>
       <c r="E39" t="n">
-        <v>1.7373</v>
+        <v>1.733</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1529</v>
+        <v>1.1486</v>
       </c>
       <c r="G39" t="n">
         <v>0.5844</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1529</v>
+        <v>1.1486</v>
       </c>
       <c r="I39" t="n">
         <v>1.1583</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5093</v>
+        <v>1.5074</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3119</v>
+        <v>0.3115</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1884</v>
+        <v>0.1566</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5093</v>
+        <v>1.5074</v>
       </c>
       <c r="F40" t="n">
-        <v>1.6567</v>
+        <v>1.5074</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1474</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.6567</v>
+        <v>1.5074</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6644</v>
+        <v>1.5074</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1474</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="L40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.517</v>
+        <v>1.5074</v>
       </c>
       <c r="N40" t="n">
-        <v>287</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.5074</v>
+        <v>1.5031</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3115</v>
+        <v>0.3106</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1876</v>
+        <v>0.1549</v>
       </c>
       <c r="E41" t="n">
-        <v>1.5074</v>
+        <v>1.5031</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5074</v>
+        <v>1.6505</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.1474</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5074</v>
+        <v>1.6505</v>
       </c>
       <c r="I41" t="n">
-        <v>1.5074</v>
+        <v>1.6644</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.1474</v>
       </c>
       <c r="K41" t="n">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>1.5074</v>
+        <v>1.517</v>
       </c>
       <c r="N41" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42">
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.4546</v>
+        <v>1.4454</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3005</v>
+        <v>0.2986</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1663</v>
+        <v>0.1319</v>
       </c>
       <c r="E42" t="n">
-        <v>1.4546</v>
+        <v>1.4454</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4546</v>
+        <v>2.4454</v>
       </c>
       <c r="G42" t="n">
         <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>2.4546</v>
+        <v>2.4454</v>
       </c>
       <c r="I42" t="n">
         <v>2.466</v>
@@ -2388,7 +2388,7 @@
         <v>0.2931</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1518</v>
+        <v>0.1213</v>
       </c>
       <c r="E43" t="n">
         <v>1.4187</v>
@@ -2434,7 +2434,7 @@
         <v>0.2929</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1513</v>
+        <v>0.1209</v>
       </c>
       <c r="E44" t="n">
         <v>1.4176</v>
@@ -2480,7 +2480,7 @@
         <v>0.2819</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1297</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="E45" t="n">
         <v>1.3642</v>
@@ -2526,7 +2526,7 @@
         <v>0.2633</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0935</v>
+        <v>0.0638</v>
       </c>
       <c r="E46" t="n">
         <v>1.2744</v>
@@ -2572,7 +2572,7 @@
         <v>0.2219</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0125</v>
+        <v>-0.0161</v>
       </c>
       <c r="E47" t="n">
         <v>1.0739</v>
@@ -2618,7 +2618,7 @@
         <v>0.2217</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0121</v>
+        <v>-0.0164</v>
       </c>
       <c r="E48" t="n">
         <v>1.073</v>
@@ -2664,7 +2664,7 @@
         <v>0.2013</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0277</v>
+        <v>-0.0557</v>
       </c>
       <c r="E49" t="n">
         <v>0.9744</v>
@@ -2710,7 +2710,7 @@
         <v>0.1698</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1165</v>
       </c>
       <c r="E50" t="n">
         <v>0.8218</v>
@@ -2756,7 +2756,7 @@
         <v>0.127</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.173</v>
+        <v>-0.199</v>
       </c>
       <c r="E51" t="n">
         <v>0.6148</v>
@@ -2802,7 +2802,7 @@
         <v>0.1088</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2087</v>
+        <v>-0.2342</v>
       </c>
       <c r="E52" t="n">
         <v>0.5264</v>
@@ -2848,7 +2848,7 @@
         <v>0.0289</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3649</v>
+        <v>-0.3882</v>
       </c>
       <c r="E53" t="n">
         <v>0.1398</v>
@@ -2894,7 +2894,7 @@
         <v>0.0258</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3709</v>
+        <v>-0.3941</v>
       </c>
       <c r="E54" t="n">
         <v>0.125</v>
@@ -2940,7 +2940,7 @@
         <v>0.0246</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3732</v>
+        <v>-0.3965</v>
       </c>
       <c r="E55" t="n">
         <v>0.1191</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0011</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4234</v>
+        <v>-0.4459</v>
       </c>
       <c r="E56" t="n">
         <v>-0.0051</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0223</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.465</v>
+        <v>-0.4869</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1079</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0283</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4767</v>
+        <v>-0.4985</v>
       </c>
       <c r="E58" t="n">
         <v>-0.137</v>
@@ -3124,7 +3124,7 @@
         <v>-0.0547</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5283</v>
+        <v>-0.5493</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2646</v>
@@ -3170,7 +3170,7 @@
         <v>-0.0572</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5333</v>
+        <v>-0.5543</v>
       </c>
       <c r="E60" t="n">
         <v>-0.277</v>
@@ -3216,7 +3216,7 @@
         <v>-0.0709</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5599</v>
+        <v>-0.5805</v>
       </c>
       <c r="E61" t="n">
         <v>-0.3429</v>
@@ -3262,7 +3262,7 @@
         <v>-0.089</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5954</v>
+        <v>-0.6155</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4307</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6168</v>
+        <v>-0.6367</v>
       </c>
       <c r="E63" t="n">
         <v>-0.4838</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1064</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.6491</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5151</v>
@@ -3400,7 +3400,7 @@
         <v>-0.1082</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6329</v>
+        <v>-0.6525</v>
       </c>
       <c r="E65" t="n">
         <v>-0.5236</v>
@@ -3446,7 +3446,7 @@
         <v>-0.13</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6755</v>
+        <v>-0.6946</v>
       </c>
       <c r="E66" t="n">
         <v>-0.6292</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1754</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7643</v>
+        <v>-0.7821</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8489</v>
@@ -3538,7 +3538,7 @@
         <v>-0.1831</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7793</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="E68" t="n">
         <v>-0.886</v>
@@ -3584,7 +3584,7 @@
         <v>-0.2066</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E69" t="n">
         <v>-1</v>
@@ -3630,7 +3630,7 @@
         <v>-0.2744</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9578</v>
+        <v>-0.9729</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3278</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.5858</v>
+        <v>-1.5848</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3277</v>
+        <v>-0.3275</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.062</v>
+        <v>-1.0753</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.5858</v>
+        <v>-1.5848</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1458</v>
+        <v>-0.1448</v>
       </c>
       <c r="G71" t="n">
         <v>-1.44</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.1458</v>
+        <v>-0.1448</v>
       </c>
       <c r="I71" t="n">
         <v>-0.1472</v>
@@ -3722,7 +3722,7 @@
         <v>-0.3557</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1169</v>
+        <v>-1.1298</v>
       </c>
       <c r="E72" t="n">
         <v>-1.7216</v>
@@ -3768,7 +3768,7 @@
         <v>-0.3625</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1301</v>
+        <v>-1.1429</v>
       </c>
       <c r="E73" t="n">
         <v>-1.7544</v>
@@ -3814,7 +3814,7 @@
         <v>-0.3969</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1974</v>
+        <v>-1.2092</v>
       </c>
       <c r="E74" t="n">
         <v>-1.921</v>
@@ -3860,7 +3860,7 @@
         <v>-0.3989</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2013</v>
+        <v>-1.2131</v>
       </c>
       <c r="E75" t="n">
         <v>-1.9306</v>
@@ -3906,7 +3906,7 @@
         <v>-0.408</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2191</v>
+        <v>-1.2307</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9748</v>
@@ -3952,7 +3952,7 @@
         <v>-0.4304</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2628</v>
+        <v>-1.2737</v>
       </c>
       <c r="E77" t="n">
         <v>-2.0829</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.5401</v>
+        <v>-2.5276</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5248</v>
+        <v>-0.5223</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4475</v>
+        <v>-1.4509</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.5401</v>
+        <v>-2.5276</v>
       </c>
       <c r="F78" t="n">
-        <v>-3.3551</v>
+        <v>-3.3426</v>
       </c>
       <c r="G78" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-3.3551</v>
+        <v>-3.3426</v>
       </c>
       <c r="I78" t="n">
         <v>-3.3707</v>
@@ -4044,7 +4044,7 @@
         <v>-0.54</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4772</v>
+        <v>-1.4852</v>
       </c>
       <c r="E79" t="n">
         <v>-2.6136</v>
@@ -4090,7 +4090,7 @@
         <v>-0.5538</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5041</v>
+        <v>-1.5117</v>
       </c>
       <c r="E80" t="n">
         <v>-2.6803</v>
@@ -4136,7 +4136,7 @@
         <v>-0.5768</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5491</v>
+        <v>-1.5561</v>
       </c>
       <c r="E81" t="n">
         <v>-2.7916</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-5.1492</v>
+        <v>-5.1183</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.0639</v>
+        <v>-1.0575</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.5015</v>
+        <v>-2.483</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.1492</v>
+        <v>-5.1183</v>
       </c>
       <c r="F82" t="n">
-        <v>-4.1455</v>
+        <v>-4.1146</v>
       </c>
       <c r="G82" t="n">
         <v>-1.0037</v>
       </c>
       <c r="H82" t="n">
-        <v>-4.1455</v>
+        <v>-4.1146</v>
       </c>
       <c r="I82" t="n">
         <v>-4.1842</v>

--- a/database/event/8046/event_8046_evp_summary.xlsx
+++ b/database/event/8046/event_8046_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.945600000000001</v>
+        <v>10.2178</v>
       </c>
       <c r="C2" t="n">
-        <v>2.055</v>
+        <v>2.1112</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9032</v>
+        <v>3.9502</v>
       </c>
       <c r="E2" t="n">
-        <v>9.945600000000001</v>
+        <v>10.2178</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7548</v>
+        <v>3.7562</v>
       </c>
       <c r="G2" t="n">
         <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4932</v>
+        <v>5.4962</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6348</v>
+        <v>5.6378</v>
       </c>
       <c r="J2" t="n">
-        <v>8.812200000000001</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>306</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>14.447</v>
+        <v>14.4498</v>
       </c>
       <c r="N2" t="n">
         <v>520</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.4818</v>
+        <v>9.7059</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9591</v>
+        <v>2.0054</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6921</v>
+        <v>3.7216</v>
       </c>
       <c r="E3" t="n">
-        <v>9.4818</v>
+        <v>9.7059</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1563</v>
+        <v>4.1384</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3254</v>
+        <v>5.325</v>
       </c>
       <c r="H3" t="n">
-        <v>6.372</v>
+        <v>6.3327</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5362</v>
+        <v>6.4959</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3254</v>
+        <v>5.325</v>
       </c>
       <c r="K3" t="n">
         <v>306</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>11.8616</v>
+        <v>11.8209</v>
       </c>
       <c r="N3" t="n">
         <v>520</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.0112</v>
+        <v>7.3082</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4487</v>
+        <v>1.51</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5674</v>
+        <v>2.6506</v>
       </c>
       <c r="E4" t="n">
-        <v>7.0112</v>
+        <v>7.3082</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6145</v>
+        <v>4.61</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3966</v>
+        <v>2.3972</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3748</v>
+        <v>7.3649</v>
       </c>
       <c r="I4" t="n">
-        <v>7.7598</v>
+        <v>7.7494</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3966</v>
+        <v>2.3972</v>
       </c>
       <c r="K4" t="n">
         <v>353</v>
@@ -621,7 +621,7 @@
         <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>10.1564</v>
+        <v>10.1466</v>
       </c>
       <c r="N4" t="n">
         <v>441</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3877</v>
+        <v>6.4944</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3198</v>
+        <v>1.3419</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2836</v>
+        <v>2.2871</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3877</v>
+        <v>6.4944</v>
       </c>
       <c r="F5" t="n">
-        <v>4.065</v>
+        <v>4.0585</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3227</v>
+        <v>2.3225</v>
       </c>
       <c r="H5" t="n">
-        <v>6.172</v>
+        <v>6.1578</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4942</v>
+        <v>6.4793</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3227</v>
+        <v>2.3225</v>
       </c>
       <c r="K5" t="n">
         <v>266</v>
@@ -667,7 +667,7 @@
         <v>253</v>
       </c>
       <c r="M5" t="n">
-        <v>8.8169</v>
+        <v>8.8018</v>
       </c>
       <c r="N5" t="n">
         <v>519</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4788</v>
+        <v>5.378</v>
       </c>
       <c r="C6" t="n">
-        <v>1.132</v>
+        <v>1.1112</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8699</v>
+        <v>1.7884</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4788</v>
+        <v>5.378</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6883</v>
+        <v>2.6683</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7905</v>
+        <v>2.7902</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1589</v>
+        <v>3.1152</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2403</v>
+        <v>3.1955</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7905</v>
+        <v>2.7902</v>
       </c>
       <c r="K6" t="n">
         <v>306</v>
@@ -713,7 +713,7 @@
         <v>214</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0308</v>
+        <v>5.9857</v>
       </c>
       <c r="N6" t="n">
         <v>520</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3316</v>
+        <v>5.3514</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1016</v>
+        <v>1.1057</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8029</v>
+        <v>1.7765</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3316</v>
+        <v>5.3514</v>
       </c>
       <c r="F7" t="n">
-        <v>1.094</v>
+        <v>1.1113</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2376</v>
+        <v>4.2375</v>
       </c>
       <c r="H7" t="n">
-        <v>1.094</v>
+        <v>1.1113</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1511</v>
+        <v>1.1693</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2376</v>
+        <v>4.2375</v>
       </c>
       <c r="K7" t="n">
         <v>266</v>
@@ -759,7 +759,7 @@
         <v>253</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3887</v>
+        <v>5.4068</v>
       </c>
       <c r="N7" t="n">
         <v>519</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1739</v>
+        <v>5.2938</v>
       </c>
       <c r="C8" t="n">
-        <v>1.069</v>
+        <v>1.0938</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7311</v>
+        <v>1.7508</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1739</v>
+        <v>5.2938</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8312</v>
+        <v>2.8208</v>
       </c>
       <c r="G8" t="n">
         <v>2.3427</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4718</v>
+        <v>3.449</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4718</v>
+        <v>3.449</v>
       </c>
       <c r="J8" t="n">
         <v>2.3427</v>
@@ -805,7 +805,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="n">
-        <v>5.8145</v>
+        <v>5.7917</v>
       </c>
       <c r="N8" t="n">
         <v>441</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.1122</v>
+        <v>5.1891</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0563</v>
+        <v>1.0722</v>
       </c>
       <c r="D9" t="n">
-        <v>1.703</v>
+        <v>1.704</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1122</v>
+        <v>5.1891</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6326</v>
+        <v>2.6417</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4796</v>
+        <v>2.4794</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0371</v>
+        <v>3.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1956</v>
+        <v>3.2164</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4796</v>
+        <v>2.4794</v>
       </c>
       <c r="K9" t="n">
         <v>266</v>
@@ -851,7 +851,7 @@
         <v>253</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6752</v>
+        <v>5.6958</v>
       </c>
       <c r="N9" t="n">
         <v>519</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>aragornN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9163</v>
+        <v>5.0831</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0158</v>
+        <v>1.0503</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6138</v>
+        <v>1.6567</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9163</v>
+        <v>5.0831</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1901</v>
+        <v>3.3828</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7262</v>
+        <v>1.5324</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2573</v>
+        <v>4.679</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4795</v>
+        <v>4.679</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7262</v>
+        <v>1.5324</v>
       </c>
       <c r="K10" t="n">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="L10" t="n">
-        <v>253</v>
+        <v>110</v>
       </c>
       <c r="M10" t="n">
-        <v>6.2057</v>
+        <v>6.2114</v>
       </c>
       <c r="N10" t="n">
-        <v>519</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aragornN</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.9101</v>
+        <v>4.9131</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0145</v>
+        <v>1.0151</v>
       </c>
       <c r="D11" t="n">
-        <v>1.611</v>
+        <v>1.5808</v>
       </c>
       <c r="E11" t="n">
-        <v>4.9101</v>
+        <v>4.9131</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3777</v>
+        <v>3.1841</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5324</v>
+        <v>1.737</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6678</v>
+        <v>4.2441</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6678</v>
+        <v>4.4656</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5324</v>
+        <v>1.737</v>
       </c>
       <c r="K11" t="n">
-        <v>331</v>
+        <v>266</v>
       </c>
       <c r="L11" t="n">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="M11" t="n">
-        <v>6.2002</v>
+        <v>6.2026</v>
       </c>
       <c r="N11" t="n">
-        <v>441</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4606</v>
+        <v>4.8771</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9217</v>
+        <v>1.0077</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4064</v>
+        <v>1.5647</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4606</v>
+        <v>4.8771</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7942</v>
+        <v>4.4012</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6664</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7942</v>
+        <v>6.9078</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7942</v>
+        <v>6.9078</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6664</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>331</v>
+        <v>177</v>
       </c>
       <c r="L12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.460599999999999</v>
+        <v>6.9078</v>
       </c>
       <c r="N12" t="n">
-        <v>441</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.4055</v>
+        <v>4.6257</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9103</v>
+        <v>0.9558</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3813</v>
+        <v>1.4524</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4055</v>
+        <v>4.6257</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4055</v>
+        <v>0.7675</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.6664</v>
       </c>
       <c r="H13" t="n">
-        <v>6.9173</v>
+        <v>0.7675</v>
       </c>
       <c r="I13" t="n">
-        <v>6.9173</v>
+        <v>0.7675</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.6664</v>
       </c>
       <c r="K13" t="n">
-        <v>177</v>
+        <v>331</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M13" t="n">
-        <v>6.9173</v>
+        <v>4.4339</v>
       </c>
       <c r="N13" t="n">
-        <v>177</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.2942</v>
+        <v>4.511</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8873</v>
+        <v>0.9321</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3306</v>
+        <v>1.4011</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2942</v>
+        <v>4.511</v>
       </c>
       <c r="F14" t="n">
         <v>2.9845</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3097</v>
+        <v>1.3092</v>
       </c>
       <c r="H14" t="n">
         <v>3.8071</v>
@@ -1072,7 +1072,7 @@
         <v>3.8071</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3097</v>
+        <v>1.3092</v>
       </c>
       <c r="K14" t="n">
         <v>129</v>
@@ -1081,7 +1081,7 @@
         <v>60</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1168</v>
+        <v>5.1163</v>
       </c>
       <c r="N14" t="n">
         <v>189</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0027</v>
+        <v>4.4626</v>
       </c>
       <c r="C15" t="n">
-        <v>0.827</v>
+        <v>0.9221</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1979</v>
+        <v>1.3795</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0027</v>
+        <v>4.4626</v>
       </c>
       <c r="F15" t="n">
         <v>3.4532</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5495</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>4.833</v>
@@ -1118,7 +1118,7 @@
         <v>4.833</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5495</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>129</v>
@@ -1127,7 +1127,7 @@
         <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3825</v>
+        <v>5.3819</v>
       </c>
       <c r="N15" t="n">
         <v>189</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.8314</v>
+        <v>3.9223</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7916</v>
+        <v>0.8104</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1199</v>
+        <v>1.1382</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8314</v>
+        <v>3.9223</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2421</v>
+        <v>4.2341</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4107</v>
+        <v>-0.4279</v>
       </c>
       <c r="H16" t="n">
-        <v>6.5597</v>
+        <v>6.5423</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9021</v>
+        <v>6.8838</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4107</v>
+        <v>-0.4279</v>
       </c>
       <c r="K16" t="n">
         <v>353</v>
@@ -1173,7 +1173,7 @@
         <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>6.4914</v>
+        <v>6.4559</v>
       </c>
       <c r="N16" t="n">
         <v>441</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.7786</v>
+        <v>3.8754</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.8007</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0959</v>
+        <v>1.1172</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7786</v>
+        <v>3.8754</v>
       </c>
       <c r="F17" t="n">
         <v>2.1033</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6753</v>
+        <v>1.6751</v>
       </c>
       <c r="H17" t="n">
         <v>2.1033</v>
@@ -1210,7 +1210,7 @@
         <v>2.2131</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6753</v>
+        <v>1.6751</v>
       </c>
       <c r="K17" t="n">
         <v>266</v>
@@ -1219,7 +1219,7 @@
         <v>253</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8884</v>
+        <v>3.8882</v>
       </c>
       <c r="N17" t="n">
         <v>519</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.4821</v>
+        <v>3.5656</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7195</v>
+        <v>0.7367</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9609</v>
+        <v>0.9789</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4821</v>
+        <v>3.5656</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0349</v>
+        <v>3.0302</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4472</v>
+        <v>0.4474</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9175</v>
+        <v>3.9072</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0184</v>
+        <v>4.0079</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4472</v>
+        <v>0.4474</v>
       </c>
       <c r="K18" t="n">
         <v>241</v>
@@ -1265,7 +1265,7 @@
         <v>46</v>
       </c>
       <c r="M18" t="n">
-        <v>4.465599999999999</v>
+        <v>4.4553</v>
       </c>
       <c r="N18" t="n">
         <v>287</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.455</v>
+        <v>3.5182</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7139</v>
+        <v>0.7269</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9486</v>
+        <v>0.9577</v>
       </c>
       <c r="E19" t="n">
-        <v>3.455</v>
+        <v>3.5182</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6644</v>
+        <v>2.3221</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7906</v>
+        <v>1.1263</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1066</v>
+        <v>2.3575</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1066</v>
+        <v>2.3575</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7906</v>
+        <v>1.1263</v>
       </c>
       <c r="K19" t="n">
         <v>165</v>
@@ -1311,7 +1311,7 @@
         <v>63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8972</v>
+        <v>3.4838</v>
       </c>
       <c r="N19" t="n">
         <v>228</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.4484</v>
+        <v>3.5171</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7125</v>
+        <v>0.7267</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9456</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4484</v>
+        <v>3.5171</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3221</v>
+        <v>2.6644</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1263</v>
+        <v>0.7906</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3575</v>
+        <v>3.1066</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3575</v>
+        <v>3.1066</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1263</v>
+        <v>0.7906</v>
       </c>
       <c r="K20" t="n">
         <v>165</v>
@@ -1357,7 +1357,7 @@
         <v>63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4838</v>
+        <v>3.8972</v>
       </c>
       <c r="N20" t="n">
         <v>228</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.439</v>
+        <v>3.3714</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7106</v>
+        <v>0.6966</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9413</v>
+        <v>0.8921</v>
       </c>
       <c r="E21" t="n">
-        <v>3.439</v>
+        <v>3.3714</v>
       </c>
       <c r="F21" t="n">
-        <v>2.186</v>
+        <v>3.4434</v>
       </c>
       <c r="G21" t="n">
-        <v>1.253</v>
+        <v>-0.1882</v>
       </c>
       <c r="H21" t="n">
-        <v>2.186</v>
+        <v>4.8117</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2423</v>
+        <v>5.0629</v>
       </c>
       <c r="J21" t="n">
-        <v>1.253</v>
+        <v>-0.1882</v>
       </c>
       <c r="K21" t="n">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="L21" t="n">
-        <v>214</v>
+        <v>88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4953</v>
+        <v>4.8747</v>
       </c>
       <c r="N21" t="n">
-        <v>520</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.3664</v>
+        <v>3.3507</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6956</v>
+        <v>0.6923</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9083</v>
+        <v>0.8829</v>
       </c>
       <c r="E22" t="n">
-        <v>3.3664</v>
+        <v>3.3507</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3932</v>
+        <v>2.3811</v>
       </c>
       <c r="G22" t="n">
         <v>0.9732</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5131</v>
+        <v>2.4865</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5131</v>
+        <v>2.4865</v>
       </c>
       <c r="J22" t="n">
         <v>0.9732</v>
@@ -1449,7 +1449,7 @@
         <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4863</v>
+        <v>3.4597</v>
       </c>
       <c r="N22" t="n">
         <v>258</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2747</v>
+        <v>3.3003</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6766</v>
+        <v>0.6819</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8665</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2747</v>
+        <v>3.3003</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4499</v>
+        <v>2.1484</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1752</v>
+        <v>1.264</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8257</v>
+        <v>2.1484</v>
       </c>
       <c r="I23" t="n">
-        <v>5.0776</v>
+        <v>2.2038</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1752</v>
+        <v>1.264</v>
       </c>
       <c r="K23" t="n">
-        <v>353</v>
+        <v>306</v>
       </c>
       <c r="L23" t="n">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9024</v>
+        <v>3.4678</v>
       </c>
       <c r="N23" t="n">
-        <v>441</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.0488</v>
+        <v>3.1911</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6299</v>
+        <v>0.6593</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7637</v>
+        <v>0.8116</v>
       </c>
       <c r="E24" t="n">
-        <v>3.0488</v>
+        <v>3.1911</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8317</v>
+        <v>2.8322</v>
       </c>
       <c r="G24" t="n">
         <v>0.2171</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4727</v>
+        <v>3.4738</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4727</v>
+        <v>3.4738</v>
       </c>
       <c r="J24" t="n">
         <v>0.2171</v>
@@ -1541,7 +1541,7 @@
         <v>60</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6898</v>
+        <v>3.6909</v>
       </c>
       <c r="N24" t="n">
         <v>258</v>
@@ -1550,541 +1550,541 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.9733</v>
+        <v>3.0659</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6143</v>
+        <v>0.6335</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7557</v>
       </c>
       <c r="E25" t="n">
-        <v>2.9733</v>
+        <v>3.0659</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7501</v>
+        <v>2.9287</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2232</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2941</v>
+        <v>3.685</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2941</v>
+        <v>3.685</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2232</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="L25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5173</v>
+        <v>3.685</v>
       </c>
       <c r="N25" t="n">
-        <v>258</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.9352</v>
+        <v>3.046</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6065</v>
+        <v>0.6294</v>
       </c>
       <c r="D26" t="n">
-        <v>0.712</v>
+        <v>0.7468</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9352</v>
+        <v>3.046</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9352</v>
+        <v>2.7436</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.2232</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6994</v>
+        <v>3.28</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6994</v>
+        <v>3.28</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.2232</v>
       </c>
       <c r="K26" t="n">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6994</v>
+        <v>3.5032</v>
       </c>
       <c r="N26" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.9247</v>
+        <v>2.8909</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6775</v>
       </c>
       <c r="E27" t="n">
-        <v>2.9247</v>
+        <v>2.8909</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9247</v>
+        <v>2.8262</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6764</v>
+        <v>3.4607</v>
       </c>
       <c r="I27" t="n">
-        <v>3.6764</v>
+        <v>3.4607</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6764</v>
+        <v>3.4607</v>
       </c>
       <c r="N27" t="n">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8262</v>
+        <v>2.8829</v>
       </c>
       <c r="C28" t="n">
-        <v>0.584</v>
+        <v>0.5957</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6623</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8262</v>
+        <v>2.8829</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8262</v>
+        <v>2.7528</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4607</v>
+        <v>3.3001</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4607</v>
+        <v>3.3001</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4607</v>
+        <v>3.3001</v>
       </c>
       <c r="N28" t="n">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.7523</v>
+        <v>2.8617</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5687</v>
+        <v>0.5913</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6287</v>
+        <v>0.6644</v>
       </c>
       <c r="E29" t="n">
-        <v>2.7523</v>
+        <v>2.8617</v>
       </c>
       <c r="F29" t="n">
-        <v>2.7523</v>
+        <v>2.9306</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2989</v>
+        <v>3.6893</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2989</v>
+        <v>3.6893</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>177</v>
+        <v>238</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2989</v>
+        <v>3.6893</v>
       </c>
       <c r="N29" t="n">
-        <v>177</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.6245</v>
+        <v>2.8181</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5423</v>
+        <v>0.5823</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5705</v>
+        <v>0.645</v>
       </c>
       <c r="E30" t="n">
-        <v>2.6245</v>
+        <v>2.8181</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6245</v>
+        <v>2.4306</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.0193</v>
+        <v>2.5949</v>
       </c>
       <c r="I30" t="n">
-        <v>3.0193</v>
+        <v>2.5949</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.0193</v>
+        <v>2.5949</v>
       </c>
       <c r="N30" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.5022</v>
+        <v>2.676</v>
       </c>
       <c r="C31" t="n">
-        <v>0.517</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5148</v>
+        <v>0.5815</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5022</v>
+        <v>2.676</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5022</v>
+        <v>2.6301</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.7515</v>
+        <v>3.0316</v>
       </c>
       <c r="I31" t="n">
-        <v>2.7515</v>
+        <v>3.0316</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.7515</v>
+        <v>3.0316</v>
       </c>
       <c r="N31" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.4935</v>
+        <v>2.594</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5152</v>
+        <v>0.536</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5109</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4935</v>
+        <v>2.594</v>
       </c>
       <c r="F32" t="n">
-        <v>3.344</v>
+        <v>2.4972</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8505</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4.594</v>
+        <v>2.7406</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7124</v>
+        <v>2.7406</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8505</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="L32" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.861899999999999</v>
+        <v>2.7406</v>
       </c>
       <c r="N32" t="n">
-        <v>287</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.4609</v>
+        <v>2.5157</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5085</v>
+        <v>0.5198</v>
       </c>
       <c r="D33" t="n">
-        <v>0.496</v>
+        <v>0.5099</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4609</v>
+        <v>2.5157</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4609</v>
+        <v>3.3432</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>2.6611</v>
+        <v>4.5923</v>
       </c>
       <c r="I33" t="n">
-        <v>2.6611</v>
+        <v>4.7106</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>2.6611</v>
+        <v>3.860300000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>238</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.4303</v>
+        <v>2.4721</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5021</v>
+        <v>0.5108</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4821</v>
+        <v>0.4904</v>
       </c>
       <c r="E34" t="n">
-        <v>2.4303</v>
+        <v>2.4721</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4303</v>
+        <v>2.4552</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5943</v>
+        <v>2.6488</v>
       </c>
       <c r="I34" t="n">
-        <v>2.5943</v>
+        <v>2.6488</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5943</v>
+        <v>2.6488</v>
       </c>
       <c r="N34" t="n">
-        <v>181</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.406</v>
+        <v>2.357</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4971</v>
+        <v>0.487</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4711</v>
+        <v>0.439</v>
       </c>
       <c r="E35" t="n">
-        <v>2.406</v>
+        <v>2.357</v>
       </c>
       <c r="F35" t="n">
-        <v>2.406</v>
+        <v>2.3266</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5411</v>
+        <v>2.3672</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5411</v>
+        <v>2.3672</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="K35" t="n">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M35" t="n">
-        <v>2.5411</v>
+        <v>2.4148</v>
       </c>
       <c r="N35" t="n">
-        <v>269</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.3821</v>
+        <v>2.3126</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4922</v>
+        <v>0.4778</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4602</v>
+        <v>0.4192</v>
       </c>
       <c r="E36" t="n">
-        <v>2.3821</v>
+        <v>2.3126</v>
       </c>
       <c r="F36" t="n">
-        <v>2.3266</v>
+        <v>3.0612</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0555</v>
+        <v>-0.8093</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3672</v>
+        <v>3.9751</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3672</v>
+        <v>3.9751</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0555</v>
+        <v>-0.8093</v>
       </c>
       <c r="K36" t="n">
         <v>165</v>
@@ -2093,7 +2093,7 @@
         <v>63</v>
       </c>
       <c r="M36" t="n">
-        <v>2.4227</v>
+        <v>3.1658</v>
       </c>
       <c r="N36" t="n">
         <v>228</v>
@@ -2102,219 +2102,219 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>d1Ledez</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.3159</v>
+        <v>2.2989</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4785</v>
+        <v>0.475</v>
       </c>
       <c r="D37" t="n">
-        <v>0.43</v>
+        <v>0.413</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3159</v>
+        <v>2.2989</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3159</v>
+        <v>2.2306</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3438</v>
+        <v>2.2306</v>
       </c>
       <c r="I37" t="n">
-        <v>2.3438</v>
+        <v>2.2306</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.3438</v>
+        <v>2.2306</v>
       </c>
       <c r="N37" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.2519</v>
+        <v>2.2738</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4653</v>
+        <v>0.4698</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4009</v>
+        <v>0.4018</v>
       </c>
       <c r="E38" t="n">
-        <v>2.2519</v>
+        <v>2.2738</v>
       </c>
       <c r="F38" t="n">
-        <v>3.0612</v>
+        <v>2.406</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8093</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.9751</v>
+        <v>2.5411</v>
       </c>
       <c r="I38" t="n">
-        <v>3.9751</v>
+        <v>2.5411</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8093</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1658</v>
+        <v>2.5411</v>
       </c>
       <c r="N38" t="n">
-        <v>228</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.2299</v>
+        <v>2.2615</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4607</v>
+        <v>0.4673</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3909</v>
+        <v>0.3963</v>
       </c>
       <c r="E39" t="n">
-        <v>2.2299</v>
+        <v>2.2615</v>
       </c>
       <c r="F39" t="n">
-        <v>2.2299</v>
+        <v>2.7287</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.619</v>
       </c>
       <c r="H39" t="n">
-        <v>2.2299</v>
+        <v>3.2473</v>
       </c>
       <c r="I39" t="n">
-        <v>2.2299</v>
+        <v>3.331</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.619</v>
       </c>
       <c r="K39" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>2.2299</v>
+        <v>2.712</v>
       </c>
       <c r="N39" t="n">
-        <v>238</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>d1Ledez</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.2154</v>
+        <v>2.2557</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4577</v>
+        <v>0.4661</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3843</v>
+        <v>0.3938</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2154</v>
+        <v>2.2557</v>
       </c>
       <c r="F40" t="n">
-        <v>2.3266</v>
+        <v>2.3159</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1112</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.3672</v>
+        <v>2.3438</v>
       </c>
       <c r="I40" t="n">
-        <v>2.4282</v>
+        <v>2.3438</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1112</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="L40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.317</v>
+        <v>2.3438</v>
       </c>
       <c r="N40" t="n">
-        <v>287</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.106</v>
+        <v>2.1993</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4351</v>
+        <v>0.4544</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3345</v>
+        <v>0.3686</v>
       </c>
       <c r="E41" t="n">
-        <v>2.106</v>
+        <v>2.1993</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7251</v>
+        <v>2.3264</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6191</v>
+        <v>-0.1111</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2394</v>
+        <v>2.3668</v>
       </c>
       <c r="I41" t="n">
-        <v>3.3229</v>
+        <v>2.4278</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6191</v>
+        <v>-0.1111</v>
       </c>
       <c r="K41" t="n">
         <v>241</v>
@@ -2323,7 +2323,7 @@
         <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>2.7038</v>
+        <v>2.3167</v>
       </c>
       <c r="N41" t="n">
         <v>287</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.0824</v>
+        <v>2.1899</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4303</v>
+        <v>0.4525</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3237</v>
+        <v>0.3644</v>
       </c>
       <c r="E42" t="n">
-        <v>2.0824</v>
+        <v>2.1899</v>
       </c>
       <c r="F42" t="n">
-        <v>2.0824</v>
+        <v>1.9861</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0824</v>
+        <v>1.9861</v>
       </c>
       <c r="I42" t="n">
-        <v>2.0824</v>
+        <v>1.9861</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.0824</v>
+        <v>1.9861</v>
       </c>
       <c r="N42" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.0336</v>
+        <v>2.179</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4202</v>
+        <v>0.4502</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3015</v>
+        <v>0.3595</v>
       </c>
       <c r="E43" t="n">
-        <v>2.0336</v>
+        <v>2.179</v>
       </c>
       <c r="F43" t="n">
-        <v>2.0336</v>
+        <v>2.0334</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.0336</v>
+        <v>2.0334</v>
       </c>
       <c r="I43" t="n">
-        <v>2.0336</v>
+        <v>2.0334</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.0336</v>
+        <v>2.0334</v>
       </c>
       <c r="N43" t="n">
         <v>279</v>
@@ -2424,124 +2424,124 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.9861</v>
+        <v>2.0691</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4104</v>
+        <v>0.4275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2799</v>
+        <v>0.3104</v>
       </c>
       <c r="E44" t="n">
-        <v>1.9861</v>
+        <v>2.0691</v>
       </c>
       <c r="F44" t="n">
-        <v>1.9861</v>
+        <v>1.9881</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.9861</v>
+        <v>1.9881</v>
       </c>
       <c r="I44" t="n">
-        <v>1.9861</v>
+        <v>1.9881</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.9861</v>
+        <v>1.9881</v>
       </c>
       <c r="N44" t="n">
-        <v>269</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.9732</v>
+        <v>1.9832</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4077</v>
+        <v>0.4098</v>
       </c>
       <c r="D45" t="n">
-        <v>0.274</v>
+        <v>0.272</v>
       </c>
       <c r="E45" t="n">
-        <v>1.9732</v>
+        <v>1.9832</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9732</v>
+        <v>2.0823</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9732</v>
+        <v>2.0823</v>
       </c>
       <c r="I45" t="n">
-        <v>1.9732</v>
+        <v>2.0823</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.9732</v>
+        <v>2.0823</v>
       </c>
       <c r="N45" t="n">
-        <v>238</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.7746</v>
+        <v>1.7408</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3667</v>
+        <v>0.3597</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1836</v>
+        <v>0.1638</v>
       </c>
       <c r="E46" t="n">
-        <v>1.7746</v>
+        <v>1.7408</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7746</v>
+        <v>1.7051</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.7746</v>
+        <v>1.7051</v>
       </c>
       <c r="I46" t="n">
-        <v>1.7746</v>
+        <v>1.7051</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.7746</v>
+        <v>1.7051</v>
       </c>
       <c r="N46" t="n">
         <v>219</v>
@@ -2562,32 +2562,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.7051</v>
+        <v>1.7106</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3523</v>
+        <v>0.3534</v>
       </c>
       <c r="D47" t="n">
-        <v>0.152</v>
+        <v>0.1503</v>
       </c>
       <c r="E47" t="n">
-        <v>1.7051</v>
+        <v>1.7106</v>
       </c>
       <c r="F47" t="n">
-        <v>1.7051</v>
+        <v>1.7746</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.7051</v>
+        <v>1.7746</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7051</v>
+        <v>1.7746</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.7051</v>
+        <v>1.7746</v>
       </c>
       <c r="N47" t="n">
         <v>219</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5613</v>
+        <v>1.4675</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3226</v>
+        <v>0.3032</v>
       </c>
       <c r="D48" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0417</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5613</v>
+        <v>1.4675</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5613</v>
+        <v>1.5497</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5613</v>
+        <v>1.5497</v>
       </c>
       <c r="I48" t="n">
-        <v>1.5613</v>
+        <v>1.5497</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.5613</v>
+        <v>1.5497</v>
       </c>
       <c r="N48" t="n">
         <v>181</v>
@@ -2654,185 +2654,185 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.3758</v>
+        <v>1.3294</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2843</v>
+        <v>0.2747</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0021</v>
+        <v>-0.02</v>
       </c>
       <c r="E49" t="n">
-        <v>1.3758</v>
+        <v>1.3294</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.035</v>
+        <v>1.0308</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4108</v>
+        <v>0.3125</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.035</v>
+        <v>1.0308</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.035</v>
+        <v>1.0308</v>
       </c>
       <c r="J49" t="n">
-        <v>1.4108</v>
+        <v>0.3125</v>
       </c>
       <c r="K49" t="n">
-        <v>331</v>
+        <v>129</v>
       </c>
       <c r="L49" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="M49" t="n">
-        <v>1.3758</v>
+        <v>1.3433</v>
       </c>
       <c r="N49" t="n">
-        <v>441</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.3435</v>
+        <v>1.3223</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2776</v>
+        <v>0.2732</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0126</v>
+        <v>-0.0232</v>
       </c>
       <c r="E50" t="n">
-        <v>1.3435</v>
+        <v>1.3223</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0308</v>
+        <v>1.2184</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3127</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.0308</v>
+        <v>1.2184</v>
       </c>
       <c r="I50" t="n">
-        <v>1.0308</v>
+        <v>1.2184</v>
       </c>
       <c r="J50" t="n">
-        <v>0.3127</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="L50" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3435</v>
+        <v>1.2184</v>
       </c>
       <c r="N50" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.21</v>
+        <v>1.1799</v>
       </c>
       <c r="C51" t="n">
-        <v>0.25</v>
+        <v>0.2438</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0868</v>
       </c>
       <c r="E51" t="n">
-        <v>1.21</v>
+        <v>1.1799</v>
       </c>
       <c r="F51" t="n">
-        <v>1.21</v>
+        <v>1.2035</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.21</v>
+        <v>1.2035</v>
       </c>
       <c r="I51" t="n">
-        <v>1.21</v>
+        <v>1.2035</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.21</v>
+        <v>1.2035</v>
       </c>
       <c r="N51" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.2035</v>
+        <v>1.1087</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2487</v>
+        <v>0.2291</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.1186</v>
       </c>
       <c r="E52" t="n">
-        <v>1.2035</v>
+        <v>1.1087</v>
       </c>
       <c r="F52" t="n">
-        <v>1.2035</v>
+        <v>-0.0663</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1.4108</v>
       </c>
       <c r="H52" t="n">
-        <v>1.2035</v>
+        <v>-0.0663</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2035</v>
+        <v>-0.0663</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1.4108</v>
       </c>
       <c r="K52" t="n">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M52" t="n">
-        <v>1.2035</v>
+        <v>1.3445</v>
       </c>
       <c r="N52" t="n">
-        <v>269</v>
+        <v>441</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8484</v>
+        <v>0.8636</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1753</v>
+        <v>0.1784</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.238</v>
+        <v>-0.2281</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8484</v>
+        <v>0.8636</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9203</v>
+        <v>0.9217</v>
       </c>
       <c r="G53" t="n">
         <v>-0.07190000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9203</v>
+        <v>0.9217</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9203</v>
+        <v>0.9217</v>
       </c>
       <c r="J53" t="n">
         <v>-0.07190000000000001</v>
@@ -2875,7 +2875,7 @@
         <v>60</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8484</v>
+        <v>0.8498</v>
       </c>
       <c r="N53" t="n">
         <v>258</v>
@@ -2884,47 +2884,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.794</v>
+        <v>0.8139</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1641</v>
+        <v>0.1682</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2628</v>
+        <v>-0.2503</v>
       </c>
       <c r="E54" t="n">
-        <v>0.794</v>
+        <v>0.8139</v>
       </c>
       <c r="F54" t="n">
-        <v>0.794</v>
+        <v>0.5189</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.794</v>
+        <v>0.5189</v>
       </c>
       <c r="I54" t="n">
-        <v>0.794</v>
+        <v>0.5189</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.794</v>
+        <v>0.5189</v>
       </c>
       <c r="N54" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55">
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7773</v>
+        <v>0.733</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1606</v>
+        <v>0.1515</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2704</v>
+        <v>-0.2864</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7773</v>
+        <v>0.733</v>
       </c>
       <c r="F55" t="n">
-        <v>1.3333</v>
+        <v>1.378</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.556</v>
+        <v>-0.5676</v>
       </c>
       <c r="H55" t="n">
-        <v>1.3333</v>
+        <v>1.378</v>
       </c>
       <c r="I55" t="n">
-        <v>1.3677</v>
+        <v>1.4135</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.556</v>
+        <v>-0.5676</v>
       </c>
       <c r="K55" t="n">
         <v>241</v>
@@ -2967,7 +2967,7 @@
         <v>46</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8116999999999999</v>
+        <v>0.8459</v>
       </c>
       <c r="N55" t="n">
         <v>287</v>
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7506</v>
+        <v>0.6695</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1551</v>
+        <v>0.1383</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2825</v>
+        <v>-0.3148</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7506</v>
+        <v>0.6695</v>
       </c>
       <c r="F56" t="n">
         <v>0.7506</v>
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5248</v>
       </c>
       <c r="C57" t="n">
-        <v>0.128</v>
+        <v>0.1084</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3422</v>
+        <v>-0.3794</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5248</v>
       </c>
       <c r="F57" t="n">
         <v>0.6195000000000001</v>
@@ -3068,139 +3068,139 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5195</v>
+        <v>0.5173</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1073</v>
+        <v>0.1069</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.3877</v>
+        <v>-0.3828</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5195</v>
+        <v>0.5173</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5195</v>
+        <v>0.7927</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5195</v>
+        <v>0.7927</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5195</v>
+        <v>0.7927</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5195</v>
+        <v>0.7927</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4501</v>
+        <v>0.4482</v>
       </c>
       <c r="C59" t="n">
-        <v>0.093</v>
+        <v>0.0926</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4193</v>
+        <v>-0.4136</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4501</v>
+        <v>0.4482</v>
       </c>
       <c r="F59" t="n">
-        <v>1.4501</v>
+        <v>0.4459</v>
       </c>
       <c r="G59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.4501</v>
+        <v>0.4459</v>
       </c>
       <c r="I59" t="n">
-        <v>1.4501</v>
+        <v>0.4459</v>
       </c>
       <c r="J59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>165</v>
+        <v>279</v>
       </c>
       <c r="L59" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4500999999999999</v>
+        <v>0.4459</v>
       </c>
       <c r="N59" t="n">
-        <v>228</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4333</v>
+        <v>0.4308</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0895</v>
+        <v>0.089</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.427</v>
+        <v>-0.4214</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4333</v>
+        <v>0.4308</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4333</v>
+        <v>1.4501</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4333</v>
+        <v>1.4501</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4333</v>
+        <v>1.4501</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K60" t="n">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4333</v>
+        <v>0.4500999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>279</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4236</v>
+        <v>0.2773</v>
       </c>
       <c r="C61" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0573</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.4314</v>
+        <v>-0.49</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4236</v>
+        <v>0.2773</v>
       </c>
       <c r="F61" t="n">
         <v>0.4236</v>
@@ -3252,231 +3252,231 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dav1g</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.2893</v>
+        <v>0.2054</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0598</v>
+        <v>0.0424</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.4925</v>
+        <v>-0.5221</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2893</v>
+        <v>0.2054</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2893</v>
+        <v>-0.0105</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2893</v>
+        <v>-0.0105</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2893</v>
+        <v>-0.0105</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.2893</v>
+        <v>-0.0105</v>
       </c>
       <c r="N62" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>dav1g</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.2623</v>
+        <v>0.1724</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0542</v>
+        <v>0.0356</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5048</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2623</v>
+        <v>0.1724</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2623</v>
+        <v>0.2886</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2623</v>
+        <v>0.2886</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2623</v>
+        <v>0.2886</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>177</v>
+        <v>279</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.2623</v>
+        <v>0.2886</v>
       </c>
       <c r="N63" t="n">
-        <v>177</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jambo</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1521</v>
+        <v>0.0888</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0314</v>
+        <v>0.0183</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.555</v>
+        <v>-0.5742</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1521</v>
+        <v>0.0888</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="N64" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>jambo</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0098</v>
+        <v>0.0601</v>
       </c>
       <c r="C65" t="n">
-        <v>0.002</v>
+        <v>0.0124</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6197</v>
+        <v>-0.587</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0098</v>
+        <v>0.0601</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0098</v>
+        <v>0.1524</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0098</v>
+        <v>0.1524</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0098</v>
+        <v>0.1524</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0098</v>
+        <v>0.1524</v>
       </c>
       <c r="N65" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.0498</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0103</v>
+        <v>-0.0164</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6469</v>
+        <v>-0.6492</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0498</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.0498</v>
+        <v>0.2623</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.0498</v>
+        <v>0.2623</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0498</v>
+        <v>0.2623</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.0498</v>
+        <v>0.2623</v>
       </c>
       <c r="N66" t="n">
-        <v>132</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.1109</v>
+        <v>-0.3371</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0229</v>
+        <v>-0.0697</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6747</v>
+        <v>-0.7644</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1109</v>
+        <v>-0.3371</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1109</v>
+        <v>-0.1108</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1109</v>
+        <v>-0.1108</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1109</v>
+        <v>-0.1108</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.1109</v>
+        <v>-0.1108</v>
       </c>
       <c r="N67" t="n">
         <v>181</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3074</v>
+        <v>-0.3976</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0635</v>
+        <v>-0.0822</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7641</v>
+        <v>-0.7914</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3074</v>
+        <v>-0.3976</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3074</v>
+        <v>-0.2908</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3074</v>
+        <v>-0.2908</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3074</v>
+        <v>-0.2908</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3074</v>
+        <v>-0.2908</v>
       </c>
       <c r="N68" t="n">
         <v>190</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.3388</v>
+        <v>-0.4181</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7784</v>
+        <v>-0.8006</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.3388</v>
+        <v>-0.4181</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8898</v>
+        <v>-0.8556</v>
       </c>
       <c r="G69" t="n">
         <v>0.5508999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8898</v>
+        <v>-0.8556</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8898</v>
+        <v>-0.8556</v>
       </c>
       <c r="J69" t="n">
         <v>0.5508999999999999</v>
@@ -3611,7 +3611,7 @@
         <v>110</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.3389000000000001</v>
+        <v>-0.3047000000000001</v>
       </c>
       <c r="N69" t="n">
         <v>441</v>
@@ -3620,415 +3620,415 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sausol</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.398</v>
+        <v>-0.5778</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.0822</v>
+        <v>-0.1194</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8054</v>
+        <v>-0.8719</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.398</v>
+        <v>-0.5778</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.398</v>
+        <v>0.7271</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-1.1798</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.398</v>
+        <v>0.7271</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.398</v>
+        <v>0.765</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-1.1798</v>
       </c>
       <c r="K70" t="n">
-        <v>279</v>
+        <v>353</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.398</v>
+        <v>-0.4147999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>sausol</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4532</v>
+        <v>-0.6188</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.0936</v>
+        <v>-0.1279</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8305</v>
+        <v>-0.8902</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.4532</v>
+        <v>-0.6188</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7271</v>
+        <v>-0.4109</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.1803</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7271</v>
+        <v>-0.4109</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7651</v>
+        <v>-0.4109</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.1803</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>353</v>
+        <v>279</v>
       </c>
       <c r="L71" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.4151999999999999</v>
+        <v>-0.4109</v>
       </c>
       <c r="N71" t="n">
-        <v>441</v>
+        <v>279</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ruggah</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1</v>
+        <v>-1.0413</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2066</v>
+        <v>-0.2152</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0794</v>
+        <v>-1.0789</v>
       </c>
       <c r="E72" t="n">
-        <v>-1</v>
+        <v>-1.0413</v>
       </c>
       <c r="F72" t="n">
-        <v>-1</v>
+        <v>-0.8135</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-0.3098</v>
       </c>
       <c r="H72" t="n">
-        <v>-1</v>
+        <v>-0.8135</v>
       </c>
       <c r="I72" t="n">
-        <v>-1</v>
+        <v>-0.8135</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-0.3098</v>
       </c>
       <c r="K72" t="n">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M72" t="n">
-        <v>-1</v>
+        <v>-1.1233</v>
       </c>
       <c r="N72" t="n">
-        <v>67</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0534</v>
+        <v>-1.2247</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2177</v>
+        <v>-0.253</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1037</v>
+        <v>-1.1609</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0534</v>
+        <v>-1.2247</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.2505</v>
+        <v>-1.1643</v>
       </c>
       <c r="G73" t="n">
-        <v>1.1971</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-2.2505</v>
+        <v>-1.1643</v>
       </c>
       <c r="I73" t="n">
-        <v>-2.3085</v>
+        <v>-1.1643</v>
       </c>
       <c r="J73" t="n">
-        <v>1.1971</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>306</v>
+        <v>132</v>
       </c>
       <c r="L73" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1114</v>
+        <v>-1.1643</v>
       </c>
       <c r="N73" t="n">
-        <v>520</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0876</v>
+        <v>-1.3047</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2247</v>
+        <v>-0.2696</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1193</v>
+        <v>-1.1966</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0876</v>
+        <v>-1.3047</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7778</v>
+        <v>-2.289</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.3098</v>
+        <v>1.1971</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7778</v>
+        <v>-2.289</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7778</v>
+        <v>-2.348</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.3098</v>
+        <v>1.1971</v>
       </c>
       <c r="K74" t="n">
-        <v>198</v>
+        <v>306</v>
       </c>
       <c r="L74" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0876</v>
+        <v>-1.1509</v>
       </c>
       <c r="N74" t="n">
-        <v>258</v>
+        <v>520</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1633</v>
+        <v>-1.359</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2404</v>
+        <v>-0.2808</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1538</v>
+        <v>-1.2209</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1633</v>
+        <v>-1.359</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1633</v>
+        <v>-0.4308</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1633</v>
+        <v>-0.4308</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1633</v>
+        <v>-0.4308</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="K75" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1633</v>
+        <v>-1.1808</v>
       </c>
       <c r="N75" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1806</v>
+        <v>-1.415</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.2439</v>
+        <v>-0.2924</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1616</v>
+        <v>-1.2459</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1806</v>
+        <v>-1.415</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.4308</v>
+        <v>-1.1943</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.7498</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.4308</v>
+        <v>-1.1943</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4308</v>
+        <v>-1.1943</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.7498</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="L76" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1806</v>
+        <v>-1.1943</v>
       </c>
       <c r="N76" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.1945</v>
+        <v>-1.438</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.2468</v>
+        <v>-0.2971</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.168</v>
+        <v>-1.2561</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.1945</v>
+        <v>-1.438</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.1945</v>
+        <v>-0.7661</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-0.4436</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.1945</v>
+        <v>-0.7661</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1945</v>
+        <v>-0.7661</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>-0.4436</v>
       </c>
       <c r="K77" t="n">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.1945</v>
+        <v>-1.2097</v>
       </c>
       <c r="N77" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>ruggah</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.2187</v>
+        <v>-1.7338</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.2518</v>
+        <v>-0.3582</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.179</v>
+        <v>-1.3883</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.2187</v>
+        <v>-1.7338</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7661</v>
+        <v>-1</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.7661</v>
+        <v>-1</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.7661</v>
+        <v>-1</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="L78" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.2187</v>
+        <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>189</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79">
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.6848</v>
+        <v>-1.9556</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.3481</v>
+        <v>-0.4041</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3912</v>
+        <v>-1.4873</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.6848</v>
+        <v>-1.9556</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.6848</v>
+        <v>-1.6846</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.6848</v>
+        <v>-1.6846</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.6848</v>
+        <v>-1.6846</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.6848</v>
+        <v>-1.6846</v>
       </c>
       <c r="N79" t="n">
         <v>177</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.8912</v>
+        <v>-2.1467</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.3908</v>
+        <v>-0.4436</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4851</v>
+        <v>-1.5727</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.8912</v>
+        <v>-2.1467</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.8912</v>
+        <v>-1.8921</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.8912</v>
+        <v>-1.8921</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8912</v>
+        <v>-1.8921</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.8912</v>
+        <v>-1.8921</v>
       </c>
       <c r="N80" t="n">
         <v>132</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.9791</v>
+        <v>-2.3921</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.4089</v>
+        <v>-0.4943</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5251</v>
+        <v>-1.6823</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.9791</v>
+        <v>-2.3921</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.9791</v>
+        <v>-1.98</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.9791</v>
+        <v>-1.98</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.9791</v>
+        <v>-1.98</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.9791</v>
+        <v>-1.98</v>
       </c>
       <c r="N81" t="n">
         <v>132</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.6751</v>
+        <v>-3.8902</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.7594</v>
+        <v>-0.8038</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.2972</v>
+        <v>-2.3515</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.6751</v>
+        <v>-3.8902</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.7223</v>
+        <v>-2.6976</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.9528</v>
+        <v>-0.9525</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.7223</v>
+        <v>-2.6976</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.8644</v>
+        <v>-2.8385</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.9528</v>
+        <v>-0.9525</v>
       </c>
       <c r="K82" t="n">
         <v>353</v>
@@ -4209,7 +4209,7 @@
         <v>88</v>
       </c>
       <c r="M82" t="n">
-        <v>-3.8172</v>
+        <v>-3.791</v>
       </c>
       <c r="N82" t="n">
         <v>441</v>
@@ -5312,13 +5312,13 @@
         <v>36</v>
       </c>
       <c r="H27" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4711</v>
+        <v>0.4819</v>
       </c>
       <c r="J27" t="n">
-        <v>16.9596</v>
+        <v>17.3484</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3077</v>
+        <v>0.3075</v>
       </c>
       <c r="J28" t="n">
-        <v>11.0772</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>1.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2051</v>
+        <v>0.205</v>
       </c>
       <c r="J29" t="n">
-        <v>7.3836</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>1.02</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0467</v>
+        <v>0.0465</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6812</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="31">
@@ -5475,10 +5475,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.241</v>
+        <v>-0.2412</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.676</v>
+        <v>-8.683199999999999</v>
       </c>
     </row>
     <row r="32">
@@ -7112,13 +7112,13 @@
         <v>21</v>
       </c>
       <c r="H72" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4201</v>
+        <v>0.4033</v>
       </c>
       <c r="J72" t="n">
-        <v>8.822100000000001</v>
+        <v>8.4693</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>1.08</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2287</v>
+        <v>0.2297</v>
       </c>
       <c r="J73" t="n">
-        <v>4.8027</v>
+        <v>4.8237</v>
       </c>
     </row>
     <row r="74">
@@ -7192,13 +7192,13 @@
         <v>21</v>
       </c>
       <c r="H74" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2287</v>
+        <v>0.2083</v>
       </c>
       <c r="J74" t="n">
-        <v>4.8027</v>
+        <v>4.3743</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.235</v>
+        <v>-0.2346</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.935</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.45</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5587</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.739</v>
+        <v>-11.7327</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.9</v>
       </c>
       <c r="I77" t="n">
-        <v>1.6072</v>
+        <v>1.6078</v>
       </c>
       <c r="J77" t="n">
-        <v>33.7512</v>
+        <v>33.7638</v>
       </c>
     </row>
     <row r="78">
@@ -7352,13 +7352,13 @@
         <v>21</v>
       </c>
       <c r="H78" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0786</v>
+        <v>1.0651</v>
       </c>
       <c r="J78" t="n">
-        <v>22.6506</v>
+        <v>22.3671</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>1.23</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6025</v>
+        <v>0.6028</v>
       </c>
       <c r="J79" t="n">
-        <v>12.6525</v>
+        <v>12.6588</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>0.87</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4678</v>
+        <v>-0.4675</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.8238</v>
+        <v>-9.817500000000001</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.612</v>
+        <v>-0.6117</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.852</v>
+        <v>-12.8457</v>
       </c>
     </row>
     <row r="82">
@@ -9912,13 +9912,13 @@
         <v>23</v>
       </c>
       <c r="H142" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5447</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>12.5281</v>
+        <v>12.3464</v>
       </c>
     </row>
     <row r="143">
@@ -10072,13 +10072,13 @@
         <v>23</v>
       </c>
       <c r="H146" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4266</v>
+        <v>-0.4179</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.8118</v>
+        <v>-9.611700000000001</v>
       </c>
     </row>
     <row r="147">
@@ -10715,10 +10715,10 @@
         <v>1.94</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8573</v>
+        <v>0.8575</v>
       </c>
       <c r="J162" t="n">
-        <v>14.5741</v>
+        <v>14.5775</v>
       </c>
     </row>
     <row r="163">
@@ -10755,10 +10755,10 @@
         <v>1.45</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5218</v>
+        <v>0.5219</v>
       </c>
       <c r="J163" t="n">
-        <v>8.8706</v>
+        <v>8.872299999999999</v>
       </c>
     </row>
     <row r="164">
@@ -10795,10 +10795,10 @@
         <v>1.33</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4285</v>
+        <v>0.4286</v>
       </c>
       <c r="J164" t="n">
-        <v>7.2845</v>
+        <v>7.2862</v>
       </c>
     </row>
     <row r="165">
@@ -10832,13 +10832,13 @@
         <v>17</v>
       </c>
       <c r="H165" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3304</v>
+        <v>0.3188</v>
       </c>
       <c r="J165" t="n">
-        <v>5.6168</v>
+        <v>5.4196</v>
       </c>
     </row>
     <row r="166">
@@ -10875,10 +10875,10 @@
         <v>1.11</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1657</v>
+        <v>0.1659</v>
       </c>
       <c r="J166" t="n">
-        <v>2.8169</v>
+        <v>2.8203</v>
       </c>
     </row>
     <row r="167">
@@ -12515,10 +12515,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.294</v>
+        <v>0.2936</v>
       </c>
       <c r="J207" t="n">
-        <v>6.174</v>
+        <v>6.1656</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.15</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2798</v>
+        <v>0.2794</v>
       </c>
       <c r="J208" t="n">
-        <v>5.8758</v>
+        <v>5.8674</v>
       </c>
     </row>
     <row r="209">
@@ -12595,10 +12595,10 @@
         <v>0.93</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1079</v>
+        <v>-0.108</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.2659</v>
+        <v>-2.268</v>
       </c>
     </row>
     <row r="210">
@@ -12632,13 +12632,13 @@
         <v>21</v>
       </c>
       <c r="H210" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1541</v>
+        <v>-0.1431</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.2361</v>
+        <v>-3.0051</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.63</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4066</v>
+        <v>-0.4068</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.538600000000001</v>
+        <v>-8.5428</v>
       </c>
     </row>
     <row r="212">
@@ -13312,13 +13312,13 @@
         <v>21</v>
       </c>
       <c r="H227" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1466</v>
+        <v>0.1291</v>
       </c>
       <c r="J227" t="n">
-        <v>3.0786</v>
+        <v>2.7111</v>
       </c>
     </row>
     <row r="228">
@@ -13355,10 +13355,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0803</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.6863</v>
+        <v>-1.6842</v>
       </c>
     </row>
     <row r="229">
@@ -13395,10 +13395,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0931</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.9593</v>
+        <v>-1.9551</v>
       </c>
     </row>
     <row r="230">
@@ -13435,10 +13435,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0931</v>
       </c>
       <c r="J230" t="n">
-        <v>-1.9593</v>
+        <v>-1.9551</v>
       </c>
     </row>
     <row r="231">
@@ -13475,10 +13475,10 @@
         <v>0.67</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3669</v>
+        <v>-0.3667</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.7049</v>
+        <v>-7.7007</v>
       </c>
     </row>
     <row r="232">
@@ -13515,10 +13515,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4861</v>
+        <v>0.4856</v>
       </c>
       <c r="J232" t="n">
-        <v>9.235900000000001</v>
+        <v>9.2264</v>
       </c>
     </row>
     <row r="233">
@@ -13555,10 +13555,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2386</v>
+        <v>0.238</v>
       </c>
       <c r="J233" t="n">
-        <v>4.5334</v>
+        <v>4.522</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>0.76</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.28</v>
+        <v>-0.2802</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.32</v>
+        <v>-5.3238</v>
       </c>
     </row>
     <row r="235">
@@ -13635,10 +13635,10 @@
         <v>0.68</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3547</v>
+        <v>-0.3549</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.7393</v>
+        <v>-6.7431</v>
       </c>
     </row>
     <row r="236">
@@ -13672,13 +13672,13 @@
         <v>19</v>
       </c>
       <c r="H236" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3639</v>
+        <v>-0.3549</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.9141</v>
+        <v>-6.7431</v>
       </c>
     </row>
     <row r="237">
@@ -13715,10 +13715,10 @@
         <v>2.07</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6428</v>
+        <v>1.6434</v>
       </c>
       <c r="J237" t="n">
-        <v>31.2132</v>
+        <v>31.2246</v>
       </c>
     </row>
     <row r="238">
@@ -13752,13 +13752,13 @@
         <v>19</v>
       </c>
       <c r="H238" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9058</v>
+        <v>0.8927</v>
       </c>
       <c r="J238" t="n">
-        <v>17.2102</v>
+        <v>16.9613</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.33</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7009</v>
+        <v>0.701</v>
       </c>
       <c r="J239" t="n">
-        <v>13.3171</v>
+        <v>13.319</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3754</v>
+        <v>-0.3751</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.1326</v>
+        <v>-7.1269</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.89</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4286</v>
+        <v>-0.4283</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.1434</v>
+        <v>-8.137700000000001</v>
       </c>
     </row>
     <row r="242">
@@ -16515,10 +16515,10 @@
         <v>1.05</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2021</v>
+        <v>0.2014</v>
       </c>
       <c r="J307" t="n">
-        <v>3.6378</v>
+        <v>3.6252</v>
       </c>
     </row>
     <row r="308">
@@ -16552,13 +16552,13 @@
         <v>18</v>
       </c>
       <c r="H308" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0495</v>
+        <v>-0.0348</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.891</v>
+        <v>-0.6264</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>0.71</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3168</v>
+        <v>-0.317</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.7024</v>
+        <v>-5.706</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>0.63</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3895</v>
+        <v>-0.3898</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.011</v>
+        <v>-7.0164</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.58</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4341</v>
+        <v>-0.4343</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.8138</v>
+        <v>-7.8174</v>
       </c>
     </row>
     <row r="312">
@@ -16715,10 +16715,10 @@
         <v>1.88</v>
       </c>
       <c r="I312" t="n">
-        <v>1.633</v>
+        <v>1.6322</v>
       </c>
       <c r="J312" t="n">
-        <v>35.926</v>
+        <v>35.9084</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6672</v>
+        <v>0.6667</v>
       </c>
       <c r="J313" t="n">
-        <v>14.6784</v>
+        <v>14.6674</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>0.96</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1897</v>
+        <v>-0.1901</v>
       </c>
       <c r="J314" t="n">
-        <v>-4.1734</v>
+        <v>-4.1822</v>
       </c>
     </row>
     <row r="315">
@@ -16832,13 +16832,13 @@
         <v>22</v>
       </c>
       <c r="H315" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4167</v>
+        <v>-0.3912</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.167400000000001</v>
+        <v>-8.606400000000001</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0372</v>
+        <v>-1.0376</v>
       </c>
       <c r="J316" t="n">
-        <v>-22.8184</v>
+        <v>-22.8272</v>
       </c>
     </row>
     <row r="317">
@@ -17315,10 +17315,10 @@
         <v>2.06</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0809</v>
+        <v>1.0812</v>
       </c>
       <c r="J327" t="n">
-        <v>17.2944</v>
+        <v>17.2992</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>1.6</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6944</v>
+        <v>0.6946</v>
       </c>
       <c r="J328" t="n">
-        <v>11.1104</v>
+        <v>11.1136</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>1.37</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4716</v>
+        <v>0.4718</v>
       </c>
       <c r="J329" t="n">
-        <v>7.5456</v>
+        <v>7.5488</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>1.11</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1651</v>
+        <v>0.1652</v>
       </c>
       <c r="J330" t="n">
-        <v>2.6416</v>
+        <v>2.6432</v>
       </c>
     </row>
     <row r="331">
@@ -17472,13 +17472,13 @@
         <v>16</v>
       </c>
       <c r="H331" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1033</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.4224</v>
+        <v>-1.6528</v>
       </c>
     </row>
     <row r="332">
@@ -18644,7 +18644,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -18915,10 +18915,10 @@
         <v>1.47</v>
       </c>
       <c r="I367" t="n">
-        <v>0.9338</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J367" t="n">
-        <v>18.676</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>0.91</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.1213</v>
+        <v>-0.121</v>
       </c>
       <c r="J368" t="n">
-        <v>-2.426</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="369">
@@ -18992,19 +18992,19 @@
         <v>20</v>
       </c>
       <c r="H369" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.2362</v>
+        <v>-0.2457</v>
       </c>
       <c r="J369" t="n">
-        <v>-4.724</v>
+        <v>-4.914</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -19035,10 +19035,10 @@
         <v>0.61</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4121</v>
+        <v>-0.4119</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.242000000000001</v>
+        <v>-8.238</v>
       </c>
     </row>
     <row r="371">
@@ -19075,10 +19075,10 @@
         <v>0.35</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6355</v>
+        <v>-0.6353</v>
       </c>
       <c r="J371" t="n">
-        <v>-12.71</v>
+        <v>-12.706</v>
       </c>
     </row>
     <row r="372">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -20449,7 +20449,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -20512,13 +20512,13 @@
         <v>24</v>
       </c>
       <c r="H407" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I407" t="n">
-        <v>0.3883</v>
+        <v>0.4007</v>
       </c>
       <c r="J407" t="n">
-        <v>9.3192</v>
+        <v>9.6168</v>
       </c>
     </row>
     <row r="408">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -20555,10 +20555,10 @@
         <v>1.11</v>
       </c>
       <c r="I408" t="n">
-        <v>0.2102</v>
+        <v>0.2099</v>
       </c>
       <c r="J408" t="n">
-        <v>5.0448</v>
+        <v>5.0376</v>
       </c>
     </row>
     <row r="409">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -20595,10 +20595,10 @@
         <v>0.98</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.044</v>
+        <v>-0.0442</v>
       </c>
       <c r="J409" t="n">
-        <v>-1.056</v>
+        <v>-1.0608</v>
       </c>
     </row>
     <row r="410">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D410" t="n">
@@ -20635,10 +20635,10 @@
         <v>0.93</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1131</v>
+        <v>-0.1133</v>
       </c>
       <c r="J410" t="n">
-        <v>-2.7144</v>
+        <v>-2.7192</v>
       </c>
     </row>
     <row r="411">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -20675,10 +20675,10 @@
         <v>0.84</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.2137</v>
+        <v>-0.2139</v>
       </c>
       <c r="J411" t="n">
-        <v>-5.1288</v>
+        <v>-5.1336</v>
       </c>
     </row>
     <row r="412">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -20894,7 +20894,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D419" t="n">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D420" t="n">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -22115,10 +22115,10 @@
         <v>1.25</v>
       </c>
       <c r="I447" t="n">
-        <v>0.6726</v>
+        <v>0.6736</v>
       </c>
       <c r="J447" t="n">
-        <v>14.7972</v>
+        <v>14.8192</v>
       </c>
     </row>
     <row r="448">
@@ -22155,10 +22155,10 @@
         <v>1.18</v>
       </c>
       <c r="I448" t="n">
-        <v>0.5173</v>
+        <v>0.5181</v>
       </c>
       <c r="J448" t="n">
-        <v>11.3806</v>
+        <v>11.3982</v>
       </c>
     </row>
     <row r="449">
@@ -22192,13 +22192,13 @@
         <v>22</v>
       </c>
       <c r="H449" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I449" t="n">
-        <v>0.2732</v>
+        <v>0.2464</v>
       </c>
       <c r="J449" t="n">
-        <v>6.0104</v>
+        <v>5.4208</v>
       </c>
     </row>
     <row r="450">
@@ -22235,10 +22235,10 @@
         <v>0.99</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0732</v>
       </c>
       <c r="J450" t="n">
-        <v>-1.6258</v>
+        <v>-1.6104</v>
       </c>
     </row>
     <row r="451">
@@ -22272,13 +22272,13 @@
         <v>22</v>
       </c>
       <c r="H451" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.1856</v>
+        <v>-0.2167</v>
       </c>
       <c r="J451" t="n">
-        <v>-4.0832</v>
+        <v>-4.7674</v>
       </c>
     </row>
     <row r="452">
@@ -22315,10 +22315,10 @@
         <v>1.05</v>
       </c>
       <c r="I452" t="n">
-        <v>0.2507</v>
+        <v>0.2473</v>
       </c>
       <c r="J452" t="n">
-        <v>4.0112</v>
+        <v>3.9568</v>
       </c>
     </row>
     <row r="453">
@@ -22352,13 +22352,13 @@
         <v>16</v>
       </c>
       <c r="H453" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I453" t="n">
-        <v>-0.1981</v>
+        <v>-0.1886</v>
       </c>
       <c r="J453" t="n">
-        <v>-3.1696</v>
+        <v>-3.0176</v>
       </c>
     </row>
     <row r="454">
@@ -22392,13 +22392,13 @@
         <v>16</v>
       </c>
       <c r="H454" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="I454" t="n">
-        <v>-0.4123</v>
+        <v>-0.3954</v>
       </c>
       <c r="J454" t="n">
-        <v>-6.5968</v>
+        <v>-6.3264</v>
       </c>
     </row>
     <row r="455">
@@ -22435,10 +22435,10 @@
         <v>0.48</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.5092</v>
+        <v>-0.51</v>
       </c>
       <c r="J455" t="n">
-        <v>-8.1472</v>
+        <v>-8.16</v>
       </c>
     </row>
     <row r="456">
@@ -22475,10 +22475,10 @@
         <v>0.47</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.518</v>
+        <v>-0.5187</v>
       </c>
       <c r="J456" t="n">
-        <v>-8.288</v>
+        <v>-8.299200000000001</v>
       </c>
     </row>
     <row r="457">
@@ -22512,13 +22512,13 @@
         <v>16</v>
       </c>
       <c r="H457" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="I457" t="n">
-        <v>1.7003</v>
+        <v>1.6895</v>
       </c>
       <c r="J457" t="n">
-        <v>27.2048</v>
+        <v>27.032</v>
       </c>
     </row>
     <row r="458">
@@ -22555,10 +22555,10 @@
         <v>1.7</v>
       </c>
       <c r="I458" t="n">
-        <v>1.3176</v>
+        <v>1.3182</v>
       </c>
       <c r="J458" t="n">
-        <v>21.0816</v>
+        <v>21.0912</v>
       </c>
     </row>
     <row r="459">
@@ -22592,13 +22592,13 @@
         <v>16</v>
       </c>
       <c r="H459" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I459" t="n">
-        <v>1.1169</v>
+        <v>1.1045</v>
       </c>
       <c r="J459" t="n">
-        <v>17.8704</v>
+        <v>17.672</v>
       </c>
     </row>
     <row r="460">
@@ -22635,10 +22635,10 @@
         <v>1.04</v>
       </c>
       <c r="I460" t="n">
-        <v>0.0969</v>
+        <v>0.0974</v>
       </c>
       <c r="J460" t="n">
-        <v>1.5504</v>
+        <v>1.5584</v>
       </c>
     </row>
     <row r="461">
@@ -22675,10 +22675,10 @@
         <v>0.99</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.1341</v>
+        <v>-0.1336</v>
       </c>
       <c r="J461" t="n">
-        <v>-2.1456</v>
+        <v>-2.1376</v>
       </c>
     </row>
     <row r="462">
@@ -23164,7 +23164,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -23712,13 +23712,13 @@
         <v>18</v>
       </c>
       <c r="H487" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I487" t="n">
-        <v>0.3179</v>
+        <v>0.3373</v>
       </c>
       <c r="J487" t="n">
-        <v>5.7222</v>
+        <v>6.0714</v>
       </c>
     </row>
     <row r="488">
@@ -23755,10 +23755,10 @@
         <v>0.97</v>
       </c>
       <c r="I488" t="n">
-        <v>-0.0416</v>
+        <v>-0.0419</v>
       </c>
       <c r="J488" t="n">
-        <v>-0.7488</v>
+        <v>-0.7542</v>
       </c>
     </row>
     <row r="489">
@@ -23795,10 +23795,10 @@
         <v>0.9</v>
       </c>
       <c r="I489" t="n">
-        <v>-0.133</v>
+        <v>-0.1332</v>
       </c>
       <c r="J489" t="n">
-        <v>-2.394</v>
+        <v>-2.3976</v>
       </c>
     </row>
     <row r="490">
@@ -23835,10 +23835,10 @@
         <v>0.73</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.3028</v>
+        <v>-0.303</v>
       </c>
       <c r="J490" t="n">
-        <v>-5.4504</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="491">
@@ -23875,10 +23875,10 @@
         <v>0.43</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.5682</v>
+        <v>-0.5684</v>
       </c>
       <c r="J491" t="n">
-        <v>-10.2276</v>
+        <v>-10.2312</v>
       </c>
     </row>
     <row r="492">
@@ -24115,10 +24115,10 @@
         <v>1.2</v>
       </c>
       <c r="I497" t="n">
-        <v>0.5553</v>
+        <v>0.5557</v>
       </c>
       <c r="J497" t="n">
-        <v>12.2166</v>
+        <v>12.2254</v>
       </c>
     </row>
     <row r="498">
@@ -24155,10 +24155,10 @@
         <v>1.15</v>
       </c>
       <c r="I498" t="n">
-        <v>0.4417</v>
+        <v>0.442</v>
       </c>
       <c r="J498" t="n">
-        <v>9.7174</v>
+        <v>9.724</v>
       </c>
     </row>
     <row r="499">
@@ -24195,10 +24195,10 @@
         <v>1.15</v>
       </c>
       <c r="I499" t="n">
-        <v>0.4417</v>
+        <v>0.442</v>
       </c>
       <c r="J499" t="n">
-        <v>9.7174</v>
+        <v>9.724</v>
       </c>
     </row>
     <row r="500">
@@ -24232,13 +24232,13 @@
         <v>22</v>
       </c>
       <c r="H500" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I500" t="n">
-        <v>0.2683</v>
+        <v>0.2409</v>
       </c>
       <c r="J500" t="n">
-        <v>5.9026</v>
+        <v>5.2998</v>
       </c>
     </row>
     <row r="501">
@@ -24275,10 +24275,10 @@
         <v>1.06</v>
       </c>
       <c r="I501" t="n">
-        <v>0.2118</v>
+        <v>0.2121</v>
       </c>
       <c r="J501" t="n">
-        <v>4.6596</v>
+        <v>4.6662</v>
       </c>
     </row>
     <row r="502">
@@ -24715,10 +24715,10 @@
         <v>1.64</v>
       </c>
       <c r="I512" t="n">
-        <v>1.07</v>
+        <v>1.0706</v>
       </c>
       <c r="J512" t="n">
-        <v>24.61</v>
+        <v>24.6238</v>
       </c>
     </row>
     <row r="513">
@@ -24752,13 +24752,13 @@
         <v>23</v>
       </c>
       <c r="H513" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I513" t="n">
-        <v>-0.1243</v>
+        <v>-0.1359</v>
       </c>
       <c r="J513" t="n">
-        <v>-2.8589</v>
+        <v>-3.1257</v>
       </c>
     </row>
     <row r="514">
@@ -24795,10 +24795,10 @@
         <v>0.86</v>
       </c>
       <c r="I514" t="n">
-        <v>-0.1916</v>
+        <v>-0.1914</v>
       </c>
       <c r="J514" t="n">
-        <v>-4.4068</v>
+        <v>-4.4022</v>
       </c>
     </row>
     <row r="515">
@@ -24835,10 +24835,10 @@
         <v>0.82</v>
       </c>
       <c r="I515" t="n">
-        <v>-0.2331</v>
+        <v>-0.2329</v>
       </c>
       <c r="J515" t="n">
-        <v>-5.3613</v>
+        <v>-5.3567</v>
       </c>
     </row>
     <row r="516">
@@ -24875,10 +24875,10 @@
         <v>0.8</v>
       </c>
       <c r="I516" t="n">
-        <v>-0.2531</v>
+        <v>-0.253</v>
       </c>
       <c r="J516" t="n">
-        <v>-5.8213</v>
+        <v>-5.819</v>
       </c>
     </row>
     <row r="517">
@@ -26715,10 +26715,10 @@
         <v>1.3</v>
       </c>
       <c r="I562" t="n">
-        <v>0.602</v>
+        <v>0.6014</v>
       </c>
       <c r="J562" t="n">
-        <v>13.846</v>
+        <v>13.8322</v>
       </c>
     </row>
     <row r="563">
@@ -26755,10 +26755,10 @@
         <v>1.1</v>
       </c>
       <c r="I563" t="n">
-        <v>0.2555</v>
+        <v>0.2551</v>
       </c>
       <c r="J563" t="n">
-        <v>5.8765</v>
+        <v>5.8673</v>
       </c>
     </row>
     <row r="564">
@@ -26795,10 +26795,10 @@
         <v>0.96</v>
       </c>
       <c r="I564" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J564" t="n">
-        <v>-1.6422</v>
+        <v>-1.6445</v>
       </c>
     </row>
     <row r="565">
@@ -26835,10 +26835,10 @@
         <v>0.79</v>
       </c>
       <c r="I565" t="n">
-        <v>-0.2608</v>
+        <v>-0.261</v>
       </c>
       <c r="J565" t="n">
-        <v>-5.9984</v>
+        <v>-6.003</v>
       </c>
     </row>
     <row r="566">
@@ -26872,13 +26872,13 @@
         <v>23</v>
       </c>
       <c r="H566" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I566" t="n">
-        <v>-0.2803</v>
+        <v>-0.2708</v>
       </c>
       <c r="J566" t="n">
-        <v>-6.4469</v>
+        <v>-6.2284</v>
       </c>
     </row>
     <row r="567">
@@ -27112,13 +27112,13 @@
         <v>17</v>
       </c>
       <c r="H572" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="I572" t="n">
-        <v>0.7059</v>
+        <v>0.7206</v>
       </c>
       <c r="J572" t="n">
-        <v>12.0003</v>
+        <v>12.2502</v>
       </c>
     </row>
     <row r="573">
@@ -27155,10 +27155,10 @@
         <v>1.32</v>
       </c>
       <c r="I573" t="n">
-        <v>0.6432</v>
+        <v>0.6425</v>
       </c>
       <c r="J573" t="n">
-        <v>10.9344</v>
+        <v>10.9225</v>
       </c>
     </row>
     <row r="574">
@@ -27195,10 +27195,10 @@
         <v>1</v>
       </c>
       <c r="I574" t="n">
-        <v>0.0052</v>
+        <v>0.0049</v>
       </c>
       <c r="J574" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="575">
@@ -27235,10 +27235,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I575" t="n">
-        <v>-0.4682</v>
+        <v>-0.4683</v>
       </c>
       <c r="J575" t="n">
-        <v>-7.9594</v>
+        <v>-7.9611</v>
       </c>
     </row>
     <row r="576">
@@ -27275,10 +27275,10 @@
         <v>0.53</v>
       </c>
       <c r="I576" t="n">
-        <v>-0.494</v>
+        <v>-0.4941</v>
       </c>
       <c r="J576" t="n">
-        <v>-8.398</v>
+        <v>-8.399699999999999</v>
       </c>
     </row>
     <row r="577">
@@ -27915,10 +27915,10 @@
         <v>1.11</v>
       </c>
       <c r="I592" t="n">
-        <v>0.2762</v>
+        <v>0.2766</v>
       </c>
       <c r="J592" t="n">
-        <v>8.286</v>
+        <v>8.298</v>
       </c>
     </row>
     <row r="593">
@@ -27955,10 +27955,10 @@
         <v>1.02</v>
       </c>
       <c r="I593" t="n">
-        <v>0.0762</v>
+        <v>0.0765</v>
       </c>
       <c r="J593" t="n">
-        <v>2.286</v>
+        <v>2.295</v>
       </c>
     </row>
     <row r="594">
@@ -28035,10 +28035,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I595" t="n">
-        <v>-0.0973</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J595" t="n">
-        <v>-2.919</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="596">
@@ -28072,13 +28072,13 @@
         <v>30</v>
       </c>
       <c r="H596" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I596" t="n">
-        <v>-0.2099</v>
+        <v>-0.22</v>
       </c>
       <c r="J596" t="n">
-        <v>-6.297</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="597">
@@ -28112,13 +28112,13 @@
         <v>30</v>
       </c>
       <c r="H597" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I597" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7118</v>
       </c>
       <c r="J597" t="n">
-        <v>20.73</v>
+        <v>21.354</v>
       </c>
     </row>
     <row r="598">
@@ -28155,10 +28155,10 @@
         <v>1.14</v>
       </c>
       <c r="I598" t="n">
-        <v>0.4216</v>
+        <v>0.4213</v>
       </c>
       <c r="J598" t="n">
-        <v>12.648</v>
+        <v>12.639</v>
       </c>
     </row>
     <row r="599">
@@ -28195,10 +28195,10 @@
         <v>1.08</v>
       </c>
       <c r="I599" t="n">
-        <v>0.2717</v>
+        <v>0.2715</v>
       </c>
       <c r="J599" t="n">
-        <v>8.151</v>
+        <v>8.145</v>
       </c>
     </row>
     <row r="600">
@@ -28235,10 +28235,10 @@
         <v>1.03</v>
       </c>
       <c r="I600" t="n">
-        <v>0.1208</v>
+        <v>0.1205</v>
       </c>
       <c r="J600" t="n">
-        <v>3.624</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="601">
@@ -28275,10 +28275,10 @@
         <v>1.01</v>
       </c>
       <c r="I601" t="n">
-        <v>0.0433</v>
+        <v>0.0429</v>
       </c>
       <c r="J601" t="n">
-        <v>1.299</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="602">
@@ -28715,10 +28715,10 @@
         <v>1.79</v>
       </c>
       <c r="I612" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8981</v>
       </c>
       <c r="J612" t="n">
-        <v>17.0563</v>
+        <v>17.0639</v>
       </c>
     </row>
     <row r="613">
@@ -28755,10 +28755,10 @@
         <v>1.53</v>
       </c>
       <c r="I613" t="n">
-        <v>0.6472</v>
+        <v>0.6474</v>
       </c>
       <c r="J613" t="n">
-        <v>12.2968</v>
+        <v>12.3006</v>
       </c>
     </row>
     <row r="614">
@@ -28792,13 +28792,13 @@
         <v>19</v>
       </c>
       <c r="H614" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="I614" t="n">
-        <v>0.1359</v>
+        <v>0.1207</v>
       </c>
       <c r="J614" t="n">
-        <v>2.5821</v>
+        <v>2.2933</v>
       </c>
     </row>
     <row r="615">
@@ -28835,10 +28835,10 @@
         <v>0.97</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0776</v>
       </c>
       <c r="J615" t="n">
-        <v>-1.4763</v>
+        <v>-1.4744</v>
       </c>
     </row>
     <row r="616">
@@ -28875,10 +28875,10 @@
         <v>0.9</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.1673</v>
+        <v>-0.1672</v>
       </c>
       <c r="J616" t="n">
-        <v>-3.1787</v>
+        <v>-3.1768</v>
       </c>
     </row>
     <row r="617">
@@ -29715,10 +29715,10 @@
         <v>1.35</v>
       </c>
       <c r="I637" t="n">
-        <v>0.8879</v>
+        <v>0.8885</v>
       </c>
       <c r="J637" t="n">
-        <v>26.637</v>
+        <v>26.655</v>
       </c>
     </row>
     <row r="638">
@@ -29752,13 +29752,13 @@
         <v>30</v>
       </c>
       <c r="H638" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I638" t="n">
-        <v>0.5446</v>
+        <v>0.5221</v>
       </c>
       <c r="J638" t="n">
-        <v>16.338</v>
+        <v>15.663</v>
       </c>
     </row>
     <row r="639">
@@ -29795,10 +29795,10 @@
         <v>1.03</v>
       </c>
       <c r="I639" t="n">
-        <v>0.1261</v>
+        <v>0.1264</v>
       </c>
       <c r="J639" t="n">
-        <v>3.783</v>
+        <v>3.792</v>
       </c>
     </row>
     <row r="640">
@@ -29835,10 +29835,10 @@
         <v>0.9</v>
       </c>
       <c r="I640" t="n">
-        <v>-0.3563</v>
+        <v>-0.3559</v>
       </c>
       <c r="J640" t="n">
-        <v>-10.689</v>
+        <v>-10.677</v>
       </c>
     </row>
     <row r="641">
@@ -29875,10 +29875,10 @@
         <v>0.89</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.3827</v>
+        <v>-0.3823</v>
       </c>
       <c r="J641" t="n">
-        <v>-11.481</v>
+        <v>-11.469</v>
       </c>
     </row>
     <row r="642">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D642" t="n">
@@ -29934,7 +29934,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D643" t="n">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D644" t="n">
@@ -30014,7 +30014,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D645" t="n">
@@ -30054,7 +30054,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D646" t="n">
@@ -30089,7 +30089,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -30209,7 +30209,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -30294,7 +30294,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D652" t="n">
@@ -30312,13 +30312,13 @@
         <v>16</v>
       </c>
       <c r="H652" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I652" t="n">
-        <v>0.7855</v>
+        <v>0.7966</v>
       </c>
       <c r="J652" t="n">
-        <v>12.568</v>
+        <v>12.7456</v>
       </c>
     </row>
     <row r="653">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D653" t="n">
@@ -30355,10 +30355,10 @@
         <v>0.92</v>
       </c>
       <c r="I653" t="n">
-        <v>-0.1043</v>
+        <v>-0.1046</v>
       </c>
       <c r="J653" t="n">
-        <v>-1.6688</v>
+        <v>-1.6736</v>
       </c>
     </row>
     <row r="654">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D654" t="n">
@@ -30395,10 +30395,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I654" t="n">
-        <v>-0.4526</v>
+        <v>-0.4528</v>
       </c>
       <c r="J654" t="n">
-        <v>-7.2416</v>
+        <v>-7.2448</v>
       </c>
     </row>
     <row r="655">
@@ -30414,7 +30414,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D655" t="n">
@@ -30435,10 +30435,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I655" t="n">
-        <v>-0.4526</v>
+        <v>-0.4528</v>
       </c>
       <c r="J655" t="n">
-        <v>-7.2416</v>
+        <v>-7.2448</v>
       </c>
     </row>
     <row r="656">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D656" t="n">
@@ -30475,10 +30475,10 @@
         <v>0.43</v>
       </c>
       <c r="I656" t="n">
-        <v>-0.5651</v>
+        <v>-0.5653</v>
       </c>
       <c r="J656" t="n">
-        <v>-9.041600000000001</v>
+        <v>-9.0448</v>
       </c>
     </row>
     <row r="657">
@@ -30489,7 +30489,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -30529,7 +30529,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -30649,7 +30649,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D662" t="n">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D663" t="n">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D664" t="n">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D665" t="n">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D666" t="n">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -30929,7 +30929,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -30969,7 +30969,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -31115,10 +31115,10 @@
         <v>1.35</v>
       </c>
       <c r="I672" t="n">
-        <v>0.6463</v>
+        <v>0.6459</v>
       </c>
       <c r="J672" t="n">
-        <v>15.5112</v>
+        <v>15.5016</v>
       </c>
     </row>
     <row r="673">
@@ -31152,13 +31152,13 @@
         <v>24</v>
       </c>
       <c r="H673" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I673" t="n">
-        <v>0.4287</v>
+        <v>0.4446</v>
       </c>
       <c r="J673" t="n">
-        <v>10.2888</v>
+        <v>10.6704</v>
       </c>
     </row>
     <row r="674">
@@ -31195,10 +31195,10 @@
         <v>1.17</v>
       </c>
       <c r="I674" t="n">
-        <v>0.3622</v>
+        <v>0.3619</v>
       </c>
       <c r="J674" t="n">
-        <v>8.6928</v>
+        <v>8.685600000000001</v>
       </c>
     </row>
     <row r="675">
@@ -31235,10 +31235,10 @@
         <v>1.08</v>
       </c>
       <c r="I675" t="n">
-        <v>0.1998</v>
+        <v>0.1996</v>
       </c>
       <c r="J675" t="n">
-        <v>4.7952</v>
+        <v>4.7904</v>
       </c>
     </row>
     <row r="676">
@@ -31275,10 +31275,10 @@
         <v>0.75</v>
       </c>
       <c r="I676" t="n">
-        <v>-0.3104</v>
+        <v>-0.3105</v>
       </c>
       <c r="J676" t="n">
-        <v>-7.4496</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="677">
@@ -32084,7 +32084,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -32112,19 +32112,19 @@
         <v>17</v>
       </c>
       <c r="H697" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="I697" t="n">
-        <v>-0.2367</v>
+        <v>-0.2168</v>
       </c>
       <c r="J697" t="n">
-        <v>-4.0239</v>
+        <v>-3.6856</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -32155,10 +32155,10 @@
         <v>0.78</v>
       </c>
       <c r="I698" t="n">
-        <v>-0.2367</v>
+        <v>-0.2375</v>
       </c>
       <c r="J698" t="n">
-        <v>-4.0239</v>
+        <v>-4.0375</v>
       </c>
     </row>
     <row r="699">
@@ -32195,10 +32195,10 @@
         <v>0.76</v>
       </c>
       <c r="I699" t="n">
-        <v>-0.2569</v>
+        <v>-0.2576</v>
       </c>
       <c r="J699" t="n">
-        <v>-4.3673</v>
+        <v>-4.3792</v>
       </c>
     </row>
     <row r="700">
@@ -32235,10 +32235,10 @@
         <v>0.73</v>
       </c>
       <c r="I700" t="n">
-        <v>-0.2862</v>
+        <v>-0.2868</v>
       </c>
       <c r="J700" t="n">
-        <v>-4.8654</v>
+        <v>-4.8756</v>
       </c>
     </row>
     <row r="701">
@@ -32275,10 +32275,10 @@
         <v>0.28</v>
       </c>
       <c r="I701" t="n">
-        <v>-0.681</v>
+        <v>-0.6814</v>
       </c>
       <c r="J701" t="n">
-        <v>-11.577</v>
+        <v>-11.5838</v>
       </c>
     </row>
     <row r="702">
@@ -33515,10 +33515,10 @@
         <v>1.46</v>
       </c>
       <c r="I732" t="n">
-        <v>1.0469</v>
+        <v>1.0499</v>
       </c>
       <c r="J732" t="n">
-        <v>21.9849</v>
+        <v>22.0479</v>
       </c>
     </row>
     <row r="733">
@@ -33552,13 +33552,13 @@
         <v>21</v>
       </c>
       <c r="H733" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I733" t="n">
-        <v>1.0001</v>
+        <v>0.9691</v>
       </c>
       <c r="J733" t="n">
-        <v>21.0021</v>
+        <v>20.3511</v>
       </c>
     </row>
     <row r="734">
@@ -33592,13 +33592,13 @@
         <v>21</v>
       </c>
       <c r="H734" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="I734" t="n">
-        <v>0.6911</v>
+        <v>0.652</v>
       </c>
       <c r="J734" t="n">
-        <v>14.5131</v>
+        <v>13.692</v>
       </c>
     </row>
     <row r="735">
@@ -33632,13 +33632,13 @@
         <v>21</v>
       </c>
       <c r="H735" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I735" t="n">
-        <v>0.0669</v>
+        <v>0.028</v>
       </c>
       <c r="J735" t="n">
-        <v>1.4049</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="736">
@@ -33672,13 +33672,13 @@
         <v>21</v>
       </c>
       <c r="H736" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="I736" t="n">
-        <v>-0.5321</v>
+        <v>-0.5773</v>
       </c>
       <c r="J736" t="n">
-        <v>-11.1741</v>
+        <v>-12.1233</v>
       </c>
     </row>
     <row r="737">
@@ -33712,13 +33712,13 @@
         <v>21</v>
       </c>
       <c r="H737" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I737" t="n">
-        <v>0.3528</v>
+        <v>0.3697</v>
       </c>
       <c r="J737" t="n">
-        <v>7.4088</v>
+        <v>7.7637</v>
       </c>
     </row>
     <row r="738">
@@ -33755,10 +33755,10 @@
         <v>1.02</v>
       </c>
       <c r="I738" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0891</v>
       </c>
       <c r="J738" t="n">
-        <v>1.8984</v>
+        <v>1.8711</v>
       </c>
     </row>
     <row r="739">
@@ -33795,10 +33795,10 @@
         <v>0.88</v>
       </c>
       <c r="I739" t="n">
-        <v>-0.1609</v>
+        <v>-0.1613</v>
       </c>
       <c r="J739" t="n">
-        <v>-3.3789</v>
+        <v>-3.3873</v>
       </c>
     </row>
     <row r="740">
@@ -33832,13 +33832,13 @@
         <v>21</v>
       </c>
       <c r="H740" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I740" t="n">
-        <v>-0.213</v>
+        <v>-0.2033</v>
       </c>
       <c r="J740" t="n">
-        <v>-4.473</v>
+        <v>-4.2693</v>
       </c>
     </row>
     <row r="741">
@@ -33872,13 +33872,13 @@
         <v>21</v>
       </c>
       <c r="H741" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I741" t="n">
-        <v>-0.4017</v>
+        <v>-0.3934</v>
       </c>
       <c r="J741" t="n">
-        <v>-8.435700000000001</v>
+        <v>-8.2614</v>
       </c>
     </row>
     <row r="742">
@@ -34004,7 +34004,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D762" t="n">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D763" t="n">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D764" t="n">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D765" t="n">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D766" t="n">
@@ -34889,7 +34889,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -34929,7 +34929,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -35049,7 +35049,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D772" t="n">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D773" t="n">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D774" t="n">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D775" t="n">
@@ -35254,7 +35254,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D776" t="n">
@@ -35289,7 +35289,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -35369,7 +35369,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -36204,7 +36204,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -36244,7 +36244,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -36315,10 +36315,10 @@
         <v>1.73</v>
       </c>
       <c r="I802" t="n">
-        <v>1.4413</v>
+        <v>1.4406</v>
       </c>
       <c r="J802" t="n">
-        <v>43.239</v>
+        <v>43.218</v>
       </c>
     </row>
     <row r="803">
@@ -36355,10 +36355,10 @@
         <v>1.21</v>
       </c>
       <c r="I803" t="n">
-        <v>0.5823</v>
+        <v>0.5819</v>
       </c>
       <c r="J803" t="n">
-        <v>17.469</v>
+        <v>17.457</v>
       </c>
     </row>
     <row r="804">
@@ -36392,13 +36392,13 @@
         <v>30</v>
       </c>
       <c r="H804" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I804" t="n">
-        <v>0.1208</v>
+        <v>0.1539</v>
       </c>
       <c r="J804" t="n">
-        <v>3.624</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="805">
@@ -36435,10 +36435,10 @@
         <v>0.8</v>
       </c>
       <c r="I805" t="n">
-        <v>-0.6083</v>
+        <v>-0.6087</v>
       </c>
       <c r="J805" t="n">
-        <v>-18.249</v>
+        <v>-18.261</v>
       </c>
     </row>
     <row r="806">
@@ -36475,10 +36475,10 @@
         <v>0.75</v>
       </c>
       <c r="I806" t="n">
-        <v>-0.7208</v>
+        <v>-0.7212</v>
       </c>
       <c r="J806" t="n">
-        <v>-21.624</v>
+        <v>-21.636</v>
       </c>
     </row>
     <row r="807">
@@ -36712,13 +36712,13 @@
         <v>23</v>
       </c>
       <c r="H812" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I812" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.751</v>
       </c>
       <c r="J812" t="n">
-        <v>17.4938</v>
+        <v>17.273</v>
       </c>
     </row>
     <row r="813">
@@ -36755,10 +36755,10 @@
         <v>1.3</v>
       </c>
       <c r="I813" t="n">
-        <v>0.4221</v>
+        <v>0.4224</v>
       </c>
       <c r="J813" t="n">
-        <v>9.708299999999999</v>
+        <v>9.715199999999999</v>
       </c>
     </row>
     <row r="814">
@@ -36795,10 +36795,10 @@
         <v>1.16</v>
       </c>
       <c r="I814" t="n">
-        <v>0.2552</v>
+        <v>0.2554</v>
       </c>
       <c r="J814" t="n">
-        <v>5.8696</v>
+        <v>5.8742</v>
       </c>
     </row>
     <row r="815">
@@ -36835,10 +36835,10 @@
         <v>0.88</v>
       </c>
       <c r="I815" t="n">
-        <v>-0.18</v>
+        <v>-0.1799</v>
       </c>
       <c r="J815" t="n">
-        <v>-4.14</v>
+        <v>-4.1377</v>
       </c>
     </row>
     <row r="816">
@@ -36875,10 +36875,10 @@
         <v>0.67</v>
       </c>
       <c r="I816" t="n">
-        <v>-0.385</v>
+        <v>-0.3848</v>
       </c>
       <c r="J816" t="n">
-        <v>-8.855</v>
+        <v>-8.8504</v>
       </c>
     </row>
     <row r="817">
@@ -37915,10 +37915,10 @@
         <v>1.46</v>
       </c>
       <c r="I842" t="n">
-        <v>1.0318</v>
+        <v>1.0315</v>
       </c>
       <c r="J842" t="n">
-        <v>18.5724</v>
+        <v>18.567</v>
       </c>
     </row>
     <row r="843">
@@ -37955,10 +37955,10 @@
         <v>1.4</v>
       </c>
       <c r="I843" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9316</v>
       </c>
       <c r="J843" t="n">
-        <v>16.776</v>
+        <v>16.7688</v>
       </c>
     </row>
     <row r="844">
@@ -37992,13 +37992,13 @@
         <v>18</v>
       </c>
       <c r="H844" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I844" t="n">
-        <v>0.9135</v>
+        <v>0.9316</v>
       </c>
       <c r="J844" t="n">
-        <v>16.443</v>
+        <v>16.7688</v>
       </c>
     </row>
     <row r="845">
@@ -38035,10 +38035,10 @@
         <v>1.17</v>
       </c>
       <c r="I845" t="n">
-        <v>0.4678</v>
+        <v>0.4675</v>
       </c>
       <c r="J845" t="n">
-        <v>8.420400000000001</v>
+        <v>8.414999999999999</v>
       </c>
     </row>
     <row r="846">
@@ -38075,10 +38075,10 @@
         <v>0.99</v>
       </c>
       <c r="I846" t="n">
-        <v>-0.1074</v>
+        <v>-0.1077</v>
       </c>
       <c r="J846" t="n">
-        <v>-1.9332</v>
+        <v>-1.9386</v>
       </c>
     </row>
     <row r="847">
@@ -38964,7 +38964,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -39115,10 +39115,10 @@
         <v>1.9</v>
       </c>
       <c r="I872" t="n">
-        <v>1.6061</v>
+        <v>1.6066</v>
       </c>
       <c r="J872" t="n">
-        <v>33.7281</v>
+        <v>33.7386</v>
       </c>
     </row>
     <row r="873">
@@ -39155,10 +39155,10 @@
         <v>1.65</v>
       </c>
       <c r="I873" t="n">
-        <v>1.2902</v>
+        <v>1.2907</v>
       </c>
       <c r="J873" t="n">
-        <v>27.0942</v>
+        <v>27.1047</v>
       </c>
     </row>
     <row r="874">
@@ -39192,13 +39192,13 @@
         <v>21</v>
       </c>
       <c r="H874" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I874" t="n">
-        <v>0.4001</v>
+        <v>0.3761</v>
       </c>
       <c r="J874" t="n">
-        <v>8.402100000000001</v>
+        <v>7.8981</v>
       </c>
     </row>
     <row r="875">
@@ -39235,10 +39235,10 @@
         <v>0.84</v>
       </c>
       <c r="I875" t="n">
-        <v>-0.542</v>
+        <v>-0.5417</v>
       </c>
       <c r="J875" t="n">
-        <v>-11.382</v>
+        <v>-11.3757</v>
       </c>
     </row>
     <row r="876">
@@ -39275,10 +39275,10 @@
         <v>0.79</v>
       </c>
       <c r="I876" t="n">
-        <v>-0.6584</v>
+        <v>-0.6581</v>
       </c>
       <c r="J876" t="n">
-        <v>-13.8264</v>
+        <v>-13.8201</v>
       </c>
     </row>
     <row r="877">
@@ -39324,7 +39324,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -39512,13 +39512,13 @@
         <v>28</v>
       </c>
       <c r="H882" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I882" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="J882" t="n">
-        <v>21.1848</v>
+        <v>21.588</v>
       </c>
     </row>
     <row r="883">
@@ -39555,10 +39555,10 @@
         <v>1.32</v>
       </c>
       <c r="I883" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="J883" t="n">
-        <v>17.7408</v>
+        <v>17.724</v>
       </c>
     </row>
     <row r="884">
@@ -39595,10 +39595,10 @@
         <v>0.79</v>
       </c>
       <c r="I884" t="n">
-        <v>-0.2608</v>
+        <v>-0.261</v>
       </c>
       <c r="J884" t="n">
-        <v>-7.3024</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="885">
@@ -39635,10 +39635,10 @@
         <v>0.71</v>
       </c>
       <c r="I885" t="n">
-        <v>-0.337</v>
+        <v>-0.3372</v>
       </c>
       <c r="J885" t="n">
-        <v>-9.436</v>
+        <v>-9.441599999999999</v>
       </c>
     </row>
     <row r="886">
@@ -39675,10 +39675,10 @@
         <v>0.7</v>
       </c>
       <c r="I886" t="n">
-        <v>-0.3462</v>
+        <v>-0.3464</v>
       </c>
       <c r="J886" t="n">
-        <v>-9.6936</v>
+        <v>-9.699199999999999</v>
       </c>
     </row>
     <row r="887">
@@ -39715,10 +39715,10 @@
         <v>1.89</v>
       </c>
       <c r="I887" t="n">
-        <v>1.5955</v>
+        <v>1.5967</v>
       </c>
       <c r="J887" t="n">
-        <v>44.674</v>
+        <v>44.7076</v>
       </c>
     </row>
     <row r="888">
@@ -39752,13 +39752,13 @@
         <v>28</v>
       </c>
       <c r="H888" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I888" t="n">
-        <v>1.0361</v>
+        <v>1.0217</v>
       </c>
       <c r="J888" t="n">
-        <v>29.0108</v>
+        <v>28.6076</v>
       </c>
     </row>
     <row r="889">
@@ -39795,10 +39795,10 @@
         <v>1.05</v>
       </c>
       <c r="I889" t="n">
-        <v>0.1596</v>
+        <v>0.1603</v>
       </c>
       <c r="J889" t="n">
-        <v>4.4688</v>
+        <v>4.4884</v>
       </c>
     </row>
     <row r="890">
@@ -39832,13 +39832,13 @@
         <v>28</v>
       </c>
       <c r="H890" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I890" t="n">
-        <v>-0.1449</v>
+        <v>-0.1808</v>
       </c>
       <c r="J890" t="n">
-        <v>-4.0572</v>
+        <v>-5.0624</v>
       </c>
     </row>
     <row r="891">
@@ -39875,10 +39875,10 @@
         <v>0.91</v>
       </c>
       <c r="I891" t="n">
-        <v>-0.3631</v>
+        <v>-0.3624</v>
       </c>
       <c r="J891" t="n">
-        <v>-10.1668</v>
+        <v>-10.1472</v>
       </c>
     </row>
     <row r="892">
@@ -40115,10 +40115,10 @@
         <v>1.66</v>
       </c>
       <c r="I897" t="n">
-        <v>1.2908</v>
+        <v>1.2912</v>
       </c>
       <c r="J897" t="n">
-        <v>21.9436</v>
+        <v>21.9504</v>
       </c>
     </row>
     <row r="898">
@@ -40155,10 +40155,10 @@
         <v>1.45</v>
       </c>
       <c r="I898" t="n">
-        <v>1.01</v>
+        <v>1.0103</v>
       </c>
       <c r="J898" t="n">
-        <v>17.17</v>
+        <v>17.1751</v>
       </c>
     </row>
     <row r="899">
@@ -40195,10 +40195,10 @@
         <v>1.33</v>
       </c>
       <c r="I899" t="n">
-        <v>0.7941</v>
+        <v>0.7943</v>
       </c>
       <c r="J899" t="n">
-        <v>13.4997</v>
+        <v>13.5031</v>
       </c>
     </row>
     <row r="900">
@@ -40235,10 +40235,10 @@
         <v>1.25</v>
       </c>
       <c r="I900" t="n">
-        <v>0.6363</v>
+        <v>0.6365</v>
       </c>
       <c r="J900" t="n">
-        <v>10.8171</v>
+        <v>10.8205</v>
       </c>
     </row>
     <row r="901">
@@ -40272,13 +40272,13 @@
         <v>17</v>
       </c>
       <c r="H901" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I901" t="n">
-        <v>-0.3457</v>
+        <v>-0.373</v>
       </c>
       <c r="J901" t="n">
-        <v>-5.8769</v>
+        <v>-6.341</v>
       </c>
     </row>
     <row r="902">
@@ -40512,13 +40512,13 @@
         <v>18</v>
       </c>
       <c r="H907" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I907" t="n">
-        <v>0.5586</v>
+        <v>0.5756</v>
       </c>
       <c r="J907" t="n">
-        <v>10.0548</v>
+        <v>10.3608</v>
       </c>
     </row>
     <row r="908">
@@ -40555,10 +40555,10 @@
         <v>1</v>
       </c>
       <c r="I908" t="n">
-        <v>0.056</v>
+        <v>0.0553</v>
       </c>
       <c r="J908" t="n">
-        <v>1.008</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="909">
@@ -40595,10 +40595,10 @@
         <v>0.59</v>
       </c>
       <c r="I909" t="n">
-        <v>-0.4219</v>
+        <v>-0.4222</v>
       </c>
       <c r="J909" t="n">
-        <v>-7.5942</v>
+        <v>-7.5996</v>
       </c>
     </row>
     <row r="910">
@@ -40635,10 +40635,10 @@
         <v>0.5</v>
       </c>
       <c r="I910" t="n">
-        <v>-0.501</v>
+        <v>-0.5012</v>
       </c>
       <c r="J910" t="n">
-        <v>-9.018000000000001</v>
+        <v>-9.021599999999999</v>
       </c>
     </row>
     <row r="911">
@@ -40675,10 +40675,10 @@
         <v>0.48</v>
       </c>
       <c r="I911" t="n">
-        <v>-0.5184</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J911" t="n">
-        <v>-9.331200000000001</v>
+        <v>-9.3348</v>
       </c>
     </row>
     <row r="912">
@@ -40724,7 +40724,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -40764,7 +40764,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -41169,7 +41169,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -41209,7 +41209,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -41294,7 +41294,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D927" t="n">
@@ -41334,7 +41334,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D928" t="n">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D929" t="n">
@@ -41414,7 +41414,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D930" t="n">
@@ -41454,7 +41454,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D931" t="n">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -41529,7 +41529,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -41569,7 +41569,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -41609,7 +41609,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -41649,7 +41649,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -41694,7 +41694,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D937" t="n">
@@ -41734,7 +41734,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D938" t="n">
@@ -41774,7 +41774,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D939" t="n">
@@ -41814,7 +41814,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D940" t="n">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D941" t="n">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -41969,7 +41969,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D947" t="n">
@@ -42134,7 +42134,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D948" t="n">
@@ -42174,7 +42174,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D949" t="n">
@@ -42214,7 +42214,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D950" t="n">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D951" t="n">
@@ -43915,10 +43915,10 @@
         <v>1.33</v>
       </c>
       <c r="I992" t="n">
-        <v>0.4608</v>
+        <v>0.4612</v>
       </c>
       <c r="J992" t="n">
-        <v>11.0592</v>
+        <v>11.0688</v>
       </c>
     </row>
     <row r="993">
@@ -43955,10 +43955,10 @@
         <v>1.3</v>
       </c>
       <c r="I993" t="n">
-        <v>0.4268</v>
+        <v>0.4271</v>
       </c>
       <c r="J993" t="n">
-        <v>10.2432</v>
+        <v>10.2504</v>
       </c>
     </row>
     <row r="994">
@@ -43992,13 +43992,13 @@
         <v>24</v>
       </c>
       <c r="H994" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I994" t="n">
-        <v>0.2056</v>
+        <v>0.1921</v>
       </c>
       <c r="J994" t="n">
-        <v>4.9344</v>
+        <v>4.6104</v>
       </c>
     </row>
     <row r="995">
@@ -44035,10 +44035,10 @@
         <v>0.89</v>
       </c>
       <c r="I995" t="n">
-        <v>-0.1663</v>
+        <v>-0.1661</v>
       </c>
       <c r="J995" t="n">
-        <v>-3.9912</v>
+        <v>-3.9864</v>
       </c>
     </row>
     <row r="996">
@@ -44075,10 +44075,10 @@
         <v>0.83</v>
       </c>
       <c r="I996" t="n">
-        <v>-0.2304</v>
+        <v>-0.2302</v>
       </c>
       <c r="J996" t="n">
-        <v>-5.5296</v>
+        <v>-5.5248</v>
       </c>
     </row>
     <row r="997">
@@ -44115,10 +44115,10 @@
         <v>1.6</v>
       </c>
       <c r="I997" t="n">
-        <v>0.835</v>
+        <v>0.8343</v>
       </c>
       <c r="J997" t="n">
-        <v>20.04</v>
+        <v>20.0232</v>
       </c>
     </row>
     <row r="998">
@@ -44152,13 +44152,13 @@
         <v>24</v>
       </c>
       <c r="H998" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I998" t="n">
-        <v>0.1234</v>
+        <v>0.1408</v>
       </c>
       <c r="J998" t="n">
-        <v>2.9616</v>
+        <v>3.3792</v>
       </c>
     </row>
     <row r="999">
@@ -44195,10 +44195,10 @@
         <v>0.84</v>
       </c>
       <c r="I999" t="n">
-        <v>-0.2068</v>
+        <v>-0.207</v>
       </c>
       <c r="J999" t="n">
-        <v>-4.9632</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="1000">
@@ -44235,10 +44235,10 @@
         <v>0.66</v>
       </c>
       <c r="I1000" t="n">
-        <v>-0.379</v>
+        <v>-0.3792</v>
       </c>
       <c r="J1000" t="n">
-        <v>-9.096</v>
+        <v>-9.1008</v>
       </c>
     </row>
     <row r="1001">
@@ -44275,10 +44275,10 @@
         <v>0.57</v>
       </c>
       <c r="I1001" t="n">
-        <v>-0.4586</v>
+        <v>-0.4588</v>
       </c>
       <c r="J1001" t="n">
-        <v>-11.0064</v>
+        <v>-11.0112</v>
       </c>
     </row>
     <row r="1002">
@@ -44515,10 +44515,10 @@
         <v>1.42</v>
       </c>
       <c r="I1007" t="n">
-        <v>0.9712</v>
+        <v>0.9716</v>
       </c>
       <c r="J1007" t="n">
-        <v>19.424</v>
+        <v>19.432</v>
       </c>
     </row>
     <row r="1008">
@@ -44555,10 +44555,10 @@
         <v>1.39</v>
       </c>
       <c r="I1008" t="n">
-        <v>0.9172</v>
+        <v>0.9176</v>
       </c>
       <c r="J1008" t="n">
-        <v>18.344</v>
+        <v>18.352</v>
       </c>
     </row>
     <row r="1009">
@@ -44592,13 +44592,13 @@
         <v>20</v>
       </c>
       <c r="H1009" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I1009" t="n">
-        <v>0.6636</v>
+        <v>0.6438</v>
       </c>
       <c r="J1009" t="n">
-        <v>13.272</v>
+        <v>12.876</v>
       </c>
     </row>
     <row r="1010">
@@ -44635,10 +44635,10 @@
         <v>1.18</v>
       </c>
       <c r="I1010" t="n">
-        <v>0.4935</v>
+        <v>0.4938</v>
       </c>
       <c r="J1010" t="n">
-        <v>9.869999999999999</v>
+        <v>9.875999999999999</v>
       </c>
     </row>
     <row r="1011">
@@ -44675,10 +44675,10 @@
         <v>1.06</v>
       </c>
       <c r="I1011" t="n">
-        <v>0.1892</v>
+        <v>0.1896</v>
       </c>
       <c r="J1011" t="n">
-        <v>3.784</v>
+        <v>3.792</v>
       </c>
     </row>
     <row r="1012">
